--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GEEK\Desktop\re\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB9F28-C785-43B7-8C13-B53A66EF9A90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E018D4B5-283F-4325-9236-086900B5A209}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="1545" windowWidth="24375" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="81">
   <si>
     <t>功能模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -278,6 +278,82 @@
   </si>
   <si>
     <t>书籍管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>书籍列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示书籍列表，上部分有查询表单，可以根据name、author、type字段来查询，其中name和author是模糊查询、type是下拉列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现的BUG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列表上面的表单查询，包括三个字段name、author、type，其中name和author是模糊查询、type是下拉列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示所有书籍列表表格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据条件查询书籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除书籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏删除按钮，点击按钮弹出提示，点击确认发送删除请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑书籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击弹出一个tab页面，显示的字段有id、name、author、image、summary、description、type、publish_time其中除了id不能编辑，其他都能编辑，type是下拉列表类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复书籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，如果是已经删除的，发送ajax请求恢复，如果是正常状态的书籍弹出提示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上传书籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹出tab栏，需要填写的字段有name、author、image、summary、description、type（下拉列表）、publish_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>书籍类型管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示所有书籍类型表格列表·</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示书籍类型列表，上部分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -331,7 +407,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -420,11 +496,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -450,6 +546,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -462,8 +561,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,15 +598,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>8282</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>74544</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>8282</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>49697</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>157371</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -510,7 +621,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8282" y="16648044"/>
+          <a:off x="0" y="19488979"/>
           <a:ext cx="16440978" cy="2526196"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -893,11 +1004,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="5" customWidth="1"/>
-    <col min="2" max="2" width="22.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="20.625" style="4" customWidth="1"/>
     <col min="4" max="4" width="27.75" style="4" customWidth="1"/>
     <col min="5" max="5" width="33" style="4" customWidth="1"/>
@@ -911,19 +1022,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -1025,88 +1136,78 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+    <row r="13" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>1</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="7">
         <v>43824</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>2</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="7"/>
       <c r="H13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1114,24 +1215,26 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>3</v>
-      </c>
-      <c r="B14" s="9"/>
+        <v>2</v>
+      </c>
+      <c r="B14" s="10"/>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="7"/>
+      <c r="G14" s="7">
+        <v>43825</v>
+      </c>
       <c r="H14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1139,16 +1242,16 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>4</v>
-      </c>
-      <c r="B15" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="B15" s="10"/>
       <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>23</v>
@@ -1156,7 +1259,10 @@
       <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="7">
+        <f ca="1">NOW()</f>
+        <v>43825.733589120369</v>
+      </c>
       <c r="H15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1164,17 +1270,19 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="E16" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>10</v>
@@ -1187,24 +1295,20 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>6</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="1" t="s">
@@ -1214,20 +1318,24 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>7</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="1" t="s">
@@ -1237,17 +1345,17 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>8</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
       <c r="D19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
@@ -1260,17 +1368,17 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>9</v>
-      </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+        <v>8</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>10</v>
@@ -1283,17 +1391,17 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>10</v>
-      </c>
-      <c r="B21" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
@@ -1306,19 +1414,17 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>11</v>
-      </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
       <c r="D22" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>10</v>
@@ -1331,21 +1437,19 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>12</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>45</v>
+        <v>11</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
@@ -1358,17 +1462,21 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>13</v>
-      </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="D24" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
@@ -1381,17 +1489,17 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>14</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
       <c r="D25" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>10</v>
@@ -1402,21 +1510,19 @@
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>15</v>
-      </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
       <c r="D26" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>10</v>
@@ -1428,20 +1534,20 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>16</v>
-      </c>
-      <c r="B27" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="B27" s="10"/>
       <c r="C27" s="10"/>
       <c r="D27" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>10</v>
@@ -1452,21 +1558,21 @@
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K27" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="10"/>
-      <c r="C28" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="C28" s="10"/>
       <c r="D28" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>10</v>
@@ -1479,20 +1585,18 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>18</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>60</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
       <c r="D29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E29" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="F29" s="1" t="s">
         <v>10</v>
       </c>
@@ -1504,14 +1608,22 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>19</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="F30" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,14 +1635,18 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>20</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
@@ -1542,14 +1658,187 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
+    <row r="32" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>20</v>
+      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>21</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>22</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>23</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>24</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B23:B28"/>
+  <mergeCells count="10">
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="C30:C34"/>
+    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="B24:B29"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="B17:B22"/>
-    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="C24:C29"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GEEK\Desktop\re\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E018D4B5-283F-4325-9236-086900B5A209}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF842E6-DCD4-4464-8FDC-7FCC57D1A1A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="1545" windowWidth="24375" windowHeight="12900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="95">
   <si>
     <t>功能模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -337,10 +337,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>上传书籍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>弹出tab栏，需要填写的字段有name、author、image、summary、description、type（下拉列表）、publish_time</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -353,7 +349,67 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>表格形式显示书籍类型列表，上部分</t>
+    <t>弱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件查询书籍类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增书籍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除书籍类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击弹出confirm，点击确认发送ajax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复书籍类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑书籍类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增书籍类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，如果是已经删除的，发送ajax请求恢复，如果是正常状态的书籍类型弹出提示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹出一个tab栏，显示编辑的书籍类型，显示的字段有id、name、description，其中可编辑的有name和description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示书籍类型列表，上部分表格查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name查询，并将查询结果显示到表格中去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹出一个tab栏，显示新增书籍类型页面，需要新增的字段有name和description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接列表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -546,6 +602,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -561,19 +629,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,14 +658,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>66261</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>157371</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>41414</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -621,8 +680,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="19488979"/>
-          <a:ext cx="16440978" cy="2526196"/>
+          <a:off x="0" y="29535783"/>
+          <a:ext cx="16059978" cy="2526196"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1004,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="5" customWidth="1"/>
@@ -1022,19 +1081,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -1137,19 +1196,19 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
     </row>
     <row r="12" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -1190,7 +1249,7 @@
       <c r="A13" s="1">
         <v>1</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1219,7 +1278,7 @@
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="10"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1305,7 @@
       <c r="A15" s="1">
         <v>3</v>
       </c>
-      <c r="B15" s="10"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1261,7 +1320,7 @@
       </c>
       <c r="G15" s="7">
         <f ca="1">NOW()</f>
-        <v>43825.733589120369</v>
+        <v>43825.972893865743</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>11</v>
@@ -1274,7 +1333,7 @@
       <c r="A16" s="1">
         <v>4</v>
       </c>
-      <c r="B16" s="10"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="1" t="s">
         <v>24</v>
       </c>
@@ -1299,7 +1358,7 @@
       <c r="A17" s="1">
         <v>5</v>
       </c>
-      <c r="B17" s="11"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="1" t="s">
         <v>25</v>
       </c>
@@ -1322,10 +1381,10 @@
       <c r="A18" s="1">
         <v>6</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1349,8 +1408,8 @@
       <c r="A19" s="1">
         <v>7</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="1" t="s">
         <v>33</v>
       </c>
@@ -1372,8 +1431,8 @@
       <c r="A20" s="1">
         <v>8</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="1" t="s">
         <v>34</v>
       </c>
@@ -1395,8 +1454,8 @@
       <c r="A21" s="1">
         <v>9</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="1" t="s">
         <v>36</v>
       </c>
@@ -1418,8 +1477,8 @@
       <c r="A22" s="1">
         <v>10</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="15"/>
       <c r="D22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1441,7 +1500,7 @@
       <c r="A23" s="1">
         <v>11</v>
       </c>
-      <c r="B23" s="10"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
@@ -1466,10 +1525,10 @@
       <c r="A24" s="1">
         <v>12</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1493,8 +1552,8 @@
       <c r="A25" s="1">
         <v>13</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="1" t="s">
         <v>48</v>
       </c>
@@ -1516,8 +1575,8 @@
       <c r="A26" s="1">
         <v>14</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="1" t="s">
         <v>50</v>
       </c>
@@ -1541,8 +1600,8 @@
       <c r="A27" s="1">
         <v>15</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1566,8 +1625,8 @@
       <c r="A28" s="1">
         <v>16</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
       <c r="D28" s="1" t="s">
         <v>56</v>
       </c>
@@ -1589,8 +1648,8 @@
       <c r="A29" s="1">
         <v>17</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
       <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
@@ -1612,10 +1671,10 @@
       <c r="A30" s="1">
         <v>18</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -1639,8 +1698,8 @@
       <c r="A31" s="1">
         <v>19</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="1" t="s">
         <v>69</v>
       </c>
@@ -1662,8 +1721,8 @@
       <c r="A32" s="8">
         <v>20</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
       <c r="D32" s="8" t="s">
         <v>70</v>
       </c>
@@ -1673,7 +1732,7 @@
       <c r="F32" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G32" s="18"/>
+      <c r="G32" s="10"/>
       <c r="H32" s="8" t="s">
         <v>11</v>
       </c>
@@ -1685,8 +1744,8 @@
       <c r="A33" s="1">
         <v>21</v>
       </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="1" t="s">
         <v>72</v>
       </c>
@@ -1708,8 +1767,8 @@
       <c r="A34" s="1">
         <v>22</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="11"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="15"/>
       <c r="D34" s="1" t="s">
         <v>74</v>
       </c>
@@ -1731,21 +1790,23 @@
       <c r="A35" s="1">
         <v>23</v>
       </c>
-      <c r="B35" s="11"/>
+      <c r="B35" s="15"/>
       <c r="C35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="F35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="7"/>
-      <c r="H35" s="1"/>
+      <c r="H35" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -1754,17 +1815,17 @@
       <c r="A36" s="1">
         <v>24</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>10</v>
@@ -1777,59 +1838,197 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:11" s="9" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>25</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="1:11" s="9" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>26</v>
+      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" spans="1:11" s="9" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>27</v>
+      </c>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="7"/>
+      <c r="H39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>28</v>
+      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>29</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="7"/>
+      <c r="H41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" spans="1:11" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>30</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+    </row>
+    <row r="43" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-    </row>
-    <row r="38" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B44" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="K44" s="3" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A37:K37"/>
+  <mergeCells count="12">
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="B30:B35"/>
     <mergeCell ref="B24:B29"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF842E6-DCD4-4464-8FDC-7FCC57D1A1A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F710D3FC-D336-4984-B527-E3176E45EDA6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="97">
   <si>
     <t>功能模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -410,6 +410,14 @@
   </si>
   <si>
     <t>链接列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -608,12 +616,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -621,6 +623,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1249,7 +1257,7 @@
       <c r="A13" s="1">
         <v>1</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1278,7 +1286,7 @@
       <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="14"/>
+      <c r="B14" s="12"/>
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,7 +1313,7 @@
       <c r="A15" s="1">
         <v>3</v>
       </c>
-      <c r="B15" s="14"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1320,7 +1328,7 @@
       </c>
       <c r="G15" s="7">
         <f ca="1">NOW()</f>
-        <v>43825.972893865743</v>
+        <v>43827.721732175924</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>11</v>
@@ -1333,7 +1341,7 @@
       <c r="A16" s="1">
         <v>4</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="12"/>
       <c r="C16" s="1" t="s">
         <v>24</v>
       </c>
@@ -1358,7 +1366,7 @@
       <c r="A17" s="1">
         <v>5</v>
       </c>
-      <c r="B17" s="15"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="1" t="s">
         <v>25</v>
       </c>
@@ -1381,10 +1389,10 @@
       <c r="A18" s="1">
         <v>6</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1408,8 +1416,8 @@
       <c r="A19" s="1">
         <v>7</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
       <c r="D19" s="1" t="s">
         <v>33</v>
       </c>
@@ -1431,8 +1439,8 @@
       <c r="A20" s="1">
         <v>8</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
       <c r="D20" s="1" t="s">
         <v>34</v>
       </c>
@@ -1454,8 +1462,8 @@
       <c r="A21" s="1">
         <v>9</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
       <c r="D21" s="1" t="s">
         <v>36</v>
       </c>
@@ -1477,8 +1485,8 @@
       <c r="A22" s="1">
         <v>10</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
       <c r="D22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1500,7 +1508,7 @@
       <c r="A23" s="1">
         <v>11</v>
       </c>
-      <c r="B23" s="14"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
@@ -1525,10 +1533,10 @@
       <c r="A24" s="1">
         <v>12</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="11" t="s">
         <v>45</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1552,8 +1560,8 @@
       <c r="A25" s="1">
         <v>13</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
       <c r="D25" s="1" t="s">
         <v>48</v>
       </c>
@@ -1575,8 +1583,8 @@
       <c r="A26" s="1">
         <v>14</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
       <c r="D26" s="1" t="s">
         <v>50</v>
       </c>
@@ -1600,8 +1608,8 @@
       <c r="A27" s="1">
         <v>15</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
       <c r="D27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1625,8 +1633,8 @@
       <c r="A28" s="1">
         <v>16</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
       <c r="D28" s="1" t="s">
         <v>56</v>
       </c>
@@ -1648,8 +1656,8 @@
       <c r="A29" s="1">
         <v>17</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
       <c r="D29" s="1" t="s">
         <v>58</v>
       </c>
@@ -1671,10 +1679,10 @@
       <c r="A30" s="1">
         <v>18</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -1698,8 +1706,8 @@
       <c r="A31" s="1">
         <v>19</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
       <c r="D31" s="1" t="s">
         <v>69</v>
       </c>
@@ -1721,8 +1729,8 @@
       <c r="A32" s="8">
         <v>20</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
       <c r="D32" s="8" t="s">
         <v>70</v>
       </c>
@@ -1744,8 +1752,8 @@
       <c r="A33" s="1">
         <v>21</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
       <c r="D33" s="1" t="s">
         <v>72</v>
       </c>
@@ -1767,8 +1775,8 @@
       <c r="A34" s="1">
         <v>22</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
       <c r="D34" s="1" t="s">
         <v>74</v>
       </c>
@@ -1790,7 +1798,7 @@
       <c r="A35" s="1">
         <v>23</v>
       </c>
-      <c r="B35" s="15"/>
+      <c r="B35" s="13"/>
       <c r="C35" s="1" t="s">
         <v>81</v>
       </c>
@@ -1815,10 +1823,10 @@
       <c r="A36" s="1">
         <v>24</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -1842,8 +1850,8 @@
       <c r="A37" s="1">
         <v>25</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
       <c r="D37" s="1" t="s">
         <v>80</v>
       </c>
@@ -1865,8 +1873,8 @@
       <c r="A38" s="1">
         <v>26</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
       <c r="D38" s="1" t="s">
         <v>83</v>
       </c>
@@ -1888,8 +1896,8 @@
       <c r="A39" s="1">
         <v>27</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
       <c r="D39" s="1" t="s">
         <v>85</v>
       </c>
@@ -1911,8 +1919,8 @@
       <c r="A40" s="1">
         <v>28</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="15"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="13"/>
       <c r="D40" s="1" t="s">
         <v>86</v>
       </c>
@@ -1934,7 +1942,7 @@
       <c r="A41" s="1">
         <v>29</v>
       </c>
-      <c r="B41" s="15"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="1" t="s">
         <v>87</v>
       </c>
@@ -1967,27 +1975,31 @@
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="F42" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="G42" s="7"/>
-      <c r="H42" s="1"/>
+      <c r="H42" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
     <row r="43" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
@@ -2026,11 +2038,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C36:C40"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="C30:C34"/>
-    <mergeCell ref="B30:B35"/>
     <mergeCell ref="B24:B29"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B13:B17"/>
@@ -2038,6 +2045,11 @@
     <mergeCell ref="B18:B23"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="C24:C29"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="C30:C34"/>
+    <mergeCell ref="B30:B35"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F710D3FC-D336-4984-B527-E3176E45EDA6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CD8640-AD1A-410E-85D3-2F225AC36BA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-660" yWindow="1125" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="164">
   <si>
     <t>功能模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -145,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>强</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>博客管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -293,10 +289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>发现的BUG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BUG编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -418,6 +410,282 @@
   </si>
   <si>
     <t>弱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示所有链接列表表格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示链接列表，表格上面有查询表单，表单按照name、type属性进行查询条件拼接，其中type为下拉列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name、type字段查询链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其中name为模糊查询、type为下拉列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG清单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮弹出提示，点击确认发送ajax请求删除列表，并且删除相关缓存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性有url、name、type，其中type为下拉列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作栏恢复按钮，如果是正常状态的，弹出提示，如果是已删除状态的，发送请求完成恢复状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击弹出新的tab栏，表单填写的新增的字段，包括url、name、type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接类型管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接类型列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示链接类型列表，表格上面有查询表单，通过name字段模糊查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name字段模糊查询链接类型列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除链接类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑链接类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复链接类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性只有name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增链接类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击进入新的tab页面，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name查询模糊查询角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示角色列表，表格上面有查询表单，通过name字段模糊查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name字段模糊查询角色列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性有name、description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击进入新的tab页面，需要填写的字段有name、description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间轴管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示技能列表，表格上面有查询表单，通过name、owner、precent字段模糊查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name、owner、precent字段模糊查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性有name、owner、percent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击进入新的tab页面，需要填写的字段有name、owner、percent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示用户列表，表格上面有查询表单，通过username、tel、email模糊查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据username、tel、email模糊查询用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据username、tel、email字段模糊查询用户列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间轴列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增时间轴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击进入新的tab页面，需要填写的字段有username、qq、tel、email</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性有username、qq、tel、email</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示角色列表，表格上面有查询表单，通过content字段和modify_time字段模糊查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据content字段和modify_time字段模糊查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除时间轴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编辑时间轴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性有content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复时间轴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击进入新的tab页面，需要填写的字段有content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个涉及到leanCloud相关部分，先不做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个在数据库配置项中添加相关属性，然后直接查出来即可</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -584,7 +852,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -613,7 +881,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -623,12 +897,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -641,6 +909,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,14 +940,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>66261</xdr:rowOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>182216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>41414</xdr:rowOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>157370</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -688,8 +962,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="29535783"/>
-          <a:ext cx="16059978" cy="2526196"/>
+          <a:off x="0" y="34116064"/>
+          <a:ext cx="16059978" cy="2526197"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1071,10 +1345,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="5" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="5" customWidth="1"/>
     <col min="2" max="2" width="17.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="20.625" style="4" customWidth="1"/>
     <col min="4" max="4" width="27.75" style="4" customWidth="1"/>
@@ -1138,143 +1412,208 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+    <row r="3" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="H8" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>1</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="7">
-        <v>43824</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1284,24 +1623,16 @@
     </row>
     <row r="14" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>2</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="7">
-        <v>43825</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,25 +1642,16 @@
     </row>
     <row r="15" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>3</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="7">
-        <f ca="1">NOW()</f>
-        <v>43827.721732175924</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1339,22 +1661,16 @@
     </row>
     <row r="16" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>4</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
         <v>11</v>
       </c>
@@ -1364,20 +1680,16 @@
     </row>
     <row r="17" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>5</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1387,24 +1699,16 @@
     </row>
     <row r="18" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>6</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
         <v>11</v>
       </c>
@@ -1414,20 +1718,16 @@
     </row>
     <row r="19" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>7</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
         <v>11</v>
       </c>
@@ -1437,20 +1737,16 @@
     </row>
     <row r="20" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>8</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G20" s="1"/>
       <c r="H20" s="1" t="s">
         <v>11</v>
       </c>
@@ -1460,20 +1756,16 @@
     </row>
     <row r="21" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>9</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
         <v>11</v>
       </c>
@@ -1483,20 +1775,16 @@
     </row>
     <row r="22" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>10</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
         <v>11</v>
       </c>
@@ -1506,22 +1794,16 @@
     </row>
     <row r="23" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>11</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
         <v>11</v>
       </c>
@@ -1531,24 +1813,16 @@
     </row>
     <row r="24" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>12</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>47</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
         <v>11</v>
       </c>
@@ -1557,167 +1831,189 @@
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
+      <c r="A25" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+    </row>
+    <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>14</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>52</v>
+      <c r="J26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
+        <v>1</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G27" s="7">
+        <v>43824</v>
+      </c>
       <c r="H27" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="K27" s="1"/>
     </row>
     <row r="28" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>16</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
+        <v>2</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="D28" s="1" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G28" s="7"/>
+      <c r="G28" s="7">
+        <v>43825</v>
+      </c>
       <c r="H28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="29" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>17</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="D29" s="1" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G29" s="7">
+        <v>43828</v>
+      </c>
       <c r="H29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>18</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>63</v>
+        <v>4</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G30" s="7">
+        <v>43828</v>
+      </c>
       <c r="H30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K30" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>19</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G31" s="7">
+        <v>43828</v>
+      </c>
       <c r="H31" s="1" t="s">
         <v>11</v>
       </c>
@@ -1726,44 +2022,52 @@
       <c r="K31" s="1"/>
     </row>
     <row r="32" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>20</v>
-      </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="A32" s="1">
+        <v>6</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
     </row>
     <row r="33" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>21</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="1" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G33" s="7">
+        <v>43828</v>
+      </c>
       <c r="H33" s="1" t="s">
         <v>11</v>
       </c>
@@ -1773,20 +2077,22 @@
     </row>
     <row r="34" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>22</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
+        <v>8</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
       <c r="D34" s="1" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G34" s="7">
+        <v>43828</v>
+      </c>
       <c r="H34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1796,24 +2102,24 @@
     </row>
     <row r="35" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>23</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
       <c r="D35" s="1" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="7"/>
+      <c r="G35" s="7">
+        <v>43828</v>
+      </c>
       <c r="H35" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -1821,24 +2127,22 @@
     </row>
     <row r="36" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>24</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>60</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B36" s="14"/>
+      <c r="C36" s="15"/>
       <c r="D36" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G36" s="7"/>
+      <c r="G36" s="7">
+        <v>43828</v>
+      </c>
       <c r="H36" s="1" t="s">
         <v>11</v>
       </c>
@@ -1846,24 +2150,28 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:11" s="9" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" s="9" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>25</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
+        <v>11</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="D37" s="1" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G37" s="7">
+        <v>43828</v>
+      </c>
       <c r="H37" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -1871,22 +2179,28 @@
     </row>
     <row r="38" spans="1:11" s="9" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>26</v>
-      </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>44</v>
+      </c>
       <c r="D38" s="1" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G38" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G38" s="7">
+        <v>43828</v>
+      </c>
       <c r="H38" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -1894,162 +2208,1522 @@
     </row>
     <row r="39" spans="1:11" s="9" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>27</v>
-      </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="1" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="G39" s="7">
+        <v>43828</v>
+      </c>
       <c r="H39" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>28</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
+        <v>14</v>
+      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
       <c r="D40" s="1" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="G40" s="7">
+        <v>43828</v>
+      </c>
       <c r="H40" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K40" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>29</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="1" t="s">
-        <v>87</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
       <c r="D41" s="1" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="G41" s="7">
+        <v>43828</v>
+      </c>
       <c r="H41" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="42" spans="1:11" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
-        <v>30</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="F42" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G42" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="G42" s="7">
+        <v>43828</v>
+      </c>
       <c r="H42" s="1" t="s">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="14" t="s">
-        <v>65</v>
+    <row r="43" spans="1:11" s="12" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>17</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="D43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" spans="1:11" s="12" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>18</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="E44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+    </row>
+    <row r="45" spans="1:11" s="12" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>19</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+    </row>
+    <row r="46" spans="1:11" s="12" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>20</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+    </row>
+    <row r="47" spans="1:11" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>21</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+    </row>
+    <row r="48" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>22</v>
+      </c>
+      <c r="B48" s="14"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+    </row>
+    <row r="49" spans="1:11" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>23</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+    </row>
+    <row r="50" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>24</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+    </row>
+    <row r="51" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>25</v>
+      </c>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G51" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+    </row>
+    <row r="52" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>26</v>
+      </c>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G52" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+    </row>
+    <row r="53" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>27</v>
+      </c>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G53" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+    </row>
+    <row r="54" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>28</v>
+      </c>
+      <c r="B54" s="14"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G54" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+    </row>
+    <row r="55" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>29</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G55" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+    </row>
+    <row r="56" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>30</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G56" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+    </row>
+    <row r="57" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>31</v>
+      </c>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+    </row>
+    <row r="58" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>32</v>
+      </c>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G58" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+    </row>
+    <row r="59" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>33</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G59" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+    </row>
+    <row r="60" spans="1:11" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>34</v>
+      </c>
+      <c r="B60" s="14"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G60" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" s="12" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>35</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G61" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+    </row>
+    <row r="62" spans="1:11" s="12" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>36</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G62" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+    </row>
+    <row r="63" spans="1:11" s="12" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>37</v>
+      </c>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G63" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+    </row>
+    <row r="64" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>38</v>
+      </c>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G64" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+    </row>
+    <row r="65" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>39</v>
+      </c>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G65" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+    </row>
+    <row r="66" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>40</v>
+      </c>
+      <c r="B66" s="14"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G66" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+    </row>
+    <row r="67" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>41</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+    </row>
+    <row r="68" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>42</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G68" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+    </row>
+    <row r="69" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>43</v>
+      </c>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G69" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+    </row>
+    <row r="70" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>44</v>
+      </c>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G70" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+    </row>
+    <row r="71" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>45</v>
+      </c>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G71" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+    </row>
+    <row r="72" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>46</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G72" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+    </row>
+    <row r="73" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>47</v>
+      </c>
+      <c r="B73" s="15"/>
+      <c r="C73" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G73" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+    </row>
+    <row r="74" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>48</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G74" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+    </row>
+    <row r="75" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>49</v>
+      </c>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G75" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+    </row>
+    <row r="76" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>50</v>
+      </c>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G76" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+    </row>
+    <row r="77" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>51</v>
+      </c>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G77" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+    </row>
+    <row r="78" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>52</v>
+      </c>
+      <c r="B78" s="14"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G78" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+    </row>
+    <row r="79" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>53</v>
+      </c>
+      <c r="B79" s="15"/>
+      <c r="C79" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G79" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+    </row>
+    <row r="80" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>54</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G80" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+    </row>
+    <row r="81" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>55</v>
+      </c>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G81" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+    </row>
+    <row r="82" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>56</v>
+      </c>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G82" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+    </row>
+    <row r="83" spans="1:11" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>57</v>
+      </c>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G83" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+    </row>
+    <row r="84" spans="1:11" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>58</v>
+      </c>
+      <c r="B84" s="14"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G84" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+    </row>
+    <row r="85" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>59</v>
+      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G85" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+    </row>
+    <row r="86" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>60</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G86" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+    </row>
+    <row r="87" spans="1:11" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>61</v>
+      </c>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G87" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+    </row>
+    <row r="88" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>62</v>
+      </c>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G88" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+    </row>
+    <row r="89" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>63</v>
+      </c>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G89" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+    </row>
+    <row r="90" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>64</v>
+      </c>
+      <c r="B90" s="14"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G90" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+    </row>
+    <row r="91" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>65</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G91" s="7">
+        <v>43828</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
+      <c r="K92" s="12"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93" s="11"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94" s="11"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="12"/>
+      <c r="I95" s="12"/>
+      <c r="J95" s="12"/>
+      <c r="K95" s="12"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A97" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" s="21"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="21"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="21"/>
+      <c r="I97" s="21"/>
+      <c r="J97" s="21"/>
+      <c r="K97" s="21"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D98" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E98" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F98" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G98" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H98" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I98" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J98" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="K98" s="3" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B24:B29"/>
+  <mergeCells count="24">
+    <mergeCell ref="B80:B85"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="B68:B73"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="B74:B79"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="B50:B55"/>
+    <mergeCell ref="A97:K97"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="B56:B61"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="B38:B43"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="C24:C29"/>
-    <mergeCell ref="C36:C40"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="C30:C34"/>
-    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="C38:C43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CD8640-AD1A-410E-85D3-2F225AC36BA2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05175562-E9A1-47FD-866D-998DA2C39A98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-660" yWindow="1125" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-795" yWindow="360" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="165">
   <si>
     <t>功能模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -686,6 +686,10 @@
   </si>
   <si>
     <t>这个在数据库配置项中添加相关属性，然后直接查出来即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌家童</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -899,6 +903,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -909,12 +919,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1363,19 +1367,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -1831,19 +1835,19 @@
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
@@ -1905,8 +1909,13 @@
       <c r="H27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J27" s="1" t="str">
+        <f>E28</f>
+        <v>每个数据用格子卡片形式显示</v>
+      </c>
       <c r="K27" s="1"/>
     </row>
     <row r="28" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3649,19 +3658,19 @@
       <c r="K96" s="12"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="20" t="s">
+      <c r="A97" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="21"/>
-      <c r="C97" s="21"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="21"/>
-      <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
-      <c r="I97" s="21"/>
-      <c r="J97" s="21"/>
-      <c r="K97" s="21"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="17"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="17"/>
+      <c r="H97" s="17"/>
+      <c r="I97" s="17"/>
+      <c r="J97" s="17"/>
+      <c r="K97" s="17"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
@@ -3700,6 +3709,21 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B38:B43"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="B50:B55"/>
+    <mergeCell ref="A97:K97"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="B56:B61"/>
+    <mergeCell ref="C62:C66"/>
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="C80:C84"/>
     <mergeCell ref="B86:B91"/>
@@ -3709,21 +3733,6 @@
     <mergeCell ref="C68:C72"/>
     <mergeCell ref="B74:B79"/>
     <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="B50:B55"/>
-    <mergeCell ref="A97:K97"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="B44:B49"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="B56:B61"/>
-    <mergeCell ref="C62:C66"/>
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="C38:C43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05175562-E9A1-47FD-866D-998DA2C39A98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9440AB86-921E-4906-BE27-80071AAB142E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-795" yWindow="360" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1110" yWindow="255" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="166">
   <si>
     <t>功能模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -686,6 +686,10 @@
   </si>
   <si>
     <t>这个在数据库配置项中添加相关属性，然后直接查出来即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌家童</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -903,12 +907,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -919,6 +917,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1367,19 +1371,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -1835,19 +1839,19 @@
       <c r="K24" s="1"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
@@ -1912,9 +1916,8 @@
       <c r="I27" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="J27" s="1" t="str">
-        <f>E28</f>
-        <v>每个数据用格子卡片形式显示</v>
+      <c r="J27" s="7">
+        <v>43828</v>
       </c>
       <c r="K27" s="1"/>
     </row>
@@ -1933,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G28" s="7">
         <v>43825</v>
@@ -1941,8 +1944,12 @@
       <c r="H28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
+      <c r="I28" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J28" s="7">
+        <v>43828</v>
+      </c>
       <c r="K28" s="1" t="s">
         <v>162</v>
       </c>
@@ -1970,8 +1977,12 @@
       <c r="H29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+      <c r="I29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J29" s="7">
+        <v>43828</v>
+      </c>
       <c r="K29" s="1" t="s">
         <v>163</v>
       </c>
@@ -1999,8 +2010,12 @@
       <c r="H30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
+      <c r="I30" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J30" s="7">
+        <v>43828</v>
+      </c>
       <c r="K30" s="1" t="s">
         <v>163</v>
       </c>
@@ -2026,8 +2041,12 @@
       <c r="H31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
+      <c r="I31" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J31" s="7">
+        <v>43828</v>
+      </c>
       <c r="K31" s="1"/>
     </row>
     <row r="32" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -2055,8 +2074,12 @@
       <c r="H32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
+      <c r="I32" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J32" s="7">
+        <v>43828</v>
+      </c>
       <c r="K32" s="1"/>
     </row>
     <row r="33" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.2">
@@ -2080,8 +2103,12 @@
       <c r="H33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J33" s="7">
+        <v>43829</v>
+      </c>
       <c r="K33" s="1"/>
     </row>
     <row r="34" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -2105,8 +2132,12 @@
       <c r="H34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="I34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J34" s="7">
+        <v>43830</v>
+      </c>
       <c r="K34" s="1"/>
     </row>
     <row r="35" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -2131,7 +2162,7 @@
         <v>11</v>
       </c>
       <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="J35" s="7"/>
       <c r="K35" s="1"/>
     </row>
     <row r="36" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -2156,7 +2187,7 @@
         <v>11</v>
       </c>
       <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="J36" s="7"/>
       <c r="K36" s="1"/>
     </row>
     <row r="37" spans="1:11" s="9" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3658,19 +3689,19 @@
       <c r="K96" s="12"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="17"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="17"/>
-      <c r="J97" s="17"/>
-      <c r="K97" s="17"/>
+      <c r="B97" s="21"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="21"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="21"/>
+      <c r="I97" s="21"/>
+      <c r="J97" s="21"/>
+      <c r="K97" s="21"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
@@ -3709,13 +3740,7 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C74:C78"/>
     <mergeCell ref="C50:C54"/>
     <mergeCell ref="B50:B55"/>
     <mergeCell ref="A97:K97"/>
@@ -3732,7 +3757,13 @@
     <mergeCell ref="B68:B73"/>
     <mergeCell ref="C68:C72"/>
     <mergeCell ref="B74:B79"/>
-    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="B38:B43"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="B32:B37"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="C38:C43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624AEBE9-D502-4C66-B0F7-50F2C59F650E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241D2A9C-E851-43BF-9202-762118640FDA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="945" yWindow="0" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="165">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -164,9 +164,6 @@
   </si>
   <si>
     <t>博客类型管理</t>
-  </si>
-  <si>
-    <t>博客类型列表</t>
   </si>
   <si>
     <t>显示博客所有类型列表</t>
@@ -511,6 +508,22 @@
   </si>
   <si>
     <t>点击跳转到编辑博客页面，编辑博客页面，可以编辑的字段有name、description。显示的字段有id、name、description，其中id设置为不可编辑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>待完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌家童</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>博客类型列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -683,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -709,6 +722,18 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -730,16 +755,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1183,19 +1199,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1232,7 +1248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -1270,7 +1286,7 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -1289,7 +1305,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -1308,7 +1324,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -1327,7 +1343,7 @@
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -1346,7 +1362,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -1365,7 +1381,7 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -1651,19 +1667,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1704,7 +1720,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1737,7 +1753,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="17"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1770,7 +1786,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="17"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1803,7 +1819,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="17"/>
+      <c r="B30" s="11"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1836,7 +1852,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="18"/>
+      <c r="B31" s="12"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1865,10 +1881,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1898,8 +1914,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -1927,8 +1943,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -1956,16 +1972,16 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="19" t="s">
-        <v>158</v>
+      <c r="F35" s="9" t="s">
+        <v>157</v>
       </c>
       <c r="G35" s="6">
         <v>43828</v>
@@ -1981,16 +1997,16 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="18"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F36" s="19" t="s">
-        <v>158</v>
+      <c r="F36" s="9" t="s">
+        <v>157</v>
       </c>
       <c r="G36" s="6">
         <v>43828</v>
@@ -2006,7 +2022,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="17"/>
+      <c r="B37" s="11"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2016,8 +2032,8 @@
       <c r="E37" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F37" s="19" t="s">
-        <v>159</v>
+      <c r="F37" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="G37" s="6">
         <v>43828</v>
@@ -2025,28 +2041,32 @@
       <c r="H37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
+      <c r="I37" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J37" s="6">
+        <v>43840</v>
+      </c>
       <c r="K37" s="5"/>
     </row>
     <row r="38" spans="1:11" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>159</v>
+      <c r="F38" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="G38" s="6">
         <v>43828</v>
@@ -2054,33 +2074,37 @@
       <c r="H38" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
+      <c r="I38" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J38" s="6">
+        <v>43840</v>
+      </c>
       <c r="K38" s="5"/>
     </row>
     <row r="39" spans="1:11" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
       <c r="D39" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G39" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="G39" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="19" t="s">
-        <v>160</v>
       </c>
       <c r="J39" s="6">
         <v>43839</v>
@@ -2091,83 +2115,87 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
       <c r="D40" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G40" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="G40" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>160</v>
       </c>
       <c r="J40" s="6">
         <v>43839</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
       <c r="D41" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G41" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J41" s="6">
+        <v>43840</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
       <c r="D42" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="19" t="s">
+      <c r="F42" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G42" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="G42" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>160</v>
       </c>
       <c r="J42" s="6">
         <v>43839</v>
@@ -2178,16 +2206,16 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
       <c r="D43" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>12</v>
+      <c r="F43" s="9" t="s">
+        <v>161</v>
       </c>
       <c r="G43" s="6">
         <v>43828</v>
@@ -2203,17 +2231,17 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="D44" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>12</v>
@@ -2232,13 +2260,13 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
       <c r="D45" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>12</v>
@@ -2257,13 +2285,13 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
       <c r="D46" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>12</v>
@@ -2282,13 +2310,13 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
       <c r="D47" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>12</v>
@@ -2307,13 +2335,13 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12"/>
       <c r="D48" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>12</v>
@@ -2332,15 +2360,15 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="18"/>
+      <c r="B49" s="12"/>
       <c r="C49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>12</v>
@@ -2359,17 +2387,17 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="D50" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>12</v>
@@ -2388,13 +2416,13 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
       <c r="D51" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>12</v>
@@ -2413,13 +2441,13 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
       <c r="D52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>12</v>
@@ -2438,13 +2466,13 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
       <c r="D53" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>12</v>
@@ -2463,13 +2491,13 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="12"/>
       <c r="D54" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>12</v>
@@ -2488,15 +2516,15 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="18"/>
+      <c r="B55" s="12"/>
       <c r="C55" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>12</v>
@@ -2515,17 +2543,17 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="D56" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>12</v>
@@ -2544,13 +2572,13 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
       <c r="D57" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>12</v>
@@ -2569,13 +2597,13 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
       <c r="D58" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>12</v>
@@ -2594,13 +2622,13 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
       <c r="D59" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>12</v>
@@ -2619,13 +2647,13 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="12"/>
       <c r="D60" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>12</v>
@@ -2644,15 +2672,15 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="18"/>
+      <c r="B61" s="12"/>
       <c r="C61" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>12</v>
@@ -2671,17 +2699,17 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="D62" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>12</v>
@@ -2700,13 +2728,13 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
       <c r="D63" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>12</v>
@@ -2725,13 +2753,13 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
       <c r="D64" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>12</v>
@@ -2750,13 +2778,13 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
       <c r="D65" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>12</v>
@@ -2775,13 +2803,13 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="12"/>
       <c r="D66" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>12</v>
@@ -2800,15 +2828,15 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="18"/>
+      <c r="B67" s="12"/>
       <c r="C67" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>12</v>
@@ -2827,17 +2855,17 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="D68" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>12</v>
@@ -2856,13 +2884,13 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
       <c r="D69" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>12</v>
@@ -2881,13 +2909,13 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
       <c r="D70" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>12</v>
@@ -2906,13 +2934,13 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
       <c r="D71" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>12</v>
@@ -2931,13 +2959,13 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="18"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="12"/>
       <c r="D72" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>12</v>
@@ -2956,15 +2984,15 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="18"/>
+      <c r="B73" s="12"/>
       <c r="C73" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>12</v>
@@ -2983,17 +3011,17 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="D74" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>12</v>
@@ -3012,13 +3040,13 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
       <c r="D75" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>12</v>
@@ -3037,13 +3065,13 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
       <c r="D76" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>12</v>
@@ -3062,13 +3090,13 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
       <c r="D77" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>12</v>
@@ -3087,13 +3115,13 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="18"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="12"/>
       <c r="D78" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>12</v>
@@ -3112,15 +3140,15 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="18"/>
+      <c r="B79" s="12"/>
       <c r="C79" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>12</v>
@@ -3139,17 +3167,17 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="D80" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>12</v>
@@ -3168,13 +3196,13 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
       <c r="D81" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>12</v>
@@ -3193,13 +3221,13 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
       <c r="D82" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>12</v>
@@ -3218,13 +3246,13 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
       <c r="D83" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>12</v>
@@ -3243,13 +3271,13 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="12"/>
       <c r="D84" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>12</v>
@@ -3268,15 +3296,15 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="18"/>
+      <c r="B85" s="12"/>
       <c r="C85" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>12</v>
@@ -3295,17 +3323,17 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="D86" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>12</v>
@@ -3324,13 +3352,13 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
       <c r="D87" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>12</v>
@@ -3349,13 +3377,13 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
       <c r="D88" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>12</v>
@@ -3374,13 +3402,13 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
       <c r="D89" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>12</v>
@@ -3399,13 +3427,13 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="18"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="12"/>
       <c r="D90" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>12</v>
@@ -3424,15 +3452,15 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="18"/>
+      <c r="B91" s="12"/>
       <c r="C91" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>12</v>
@@ -3448,15 +3476,15 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B92" s="14"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
+      <c r="A92" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3470,24 +3498,24 @@
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G96" s="8"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A97" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="B97" s="15"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
+    <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="19"/>
+      <c r="I97" s="19"/>
+      <c r="J97" s="19"/>
+      <c r="K97" s="19"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>2</v>
@@ -3522,15 +3550,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A92:G92"/>
@@ -3547,6 +3566,15 @@
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241D2A9C-E851-43BF-9202-762118640FDA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5C4694-3CBC-4523-A895-9060AB8EB4E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="0" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="166">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -511,10 +511,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>待完成</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>凌家童</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -524,6 +520,14 @@
   </si>
   <si>
     <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作栏恢复按钮，如果是正常状态的，弹出提示，如果是已删除状态的，发送请求完成恢复状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌家童</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -725,15 +729,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -753,6 +748,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1199,19 +1203,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1667,19 +1671,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1720,7 +1724,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1753,7 +1757,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="11"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1786,7 +1790,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="11"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1819,7 +1823,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="11"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1852,7 +1856,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="12"/>
+      <c r="B31" s="19"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1881,10 +1885,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="17" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1914,8 +1918,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -1943,8 +1947,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -1972,8 +1976,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -1997,8 +2001,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="19"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2022,7 +2026,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="11"/>
+      <c r="B37" s="18"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2042,7 +2046,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J37" s="6">
         <v>43840</v>
@@ -2053,11 +2057,11 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="17" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>48</v>
@@ -2075,7 +2079,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J38" s="6">
         <v>43840</v>
@@ -2086,8 +2090,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2115,8 +2119,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2146,8 +2150,8 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
@@ -2155,7 +2159,7 @@
         <v>160</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G41" s="6">
         <v>43828</v>
@@ -2164,7 +2168,7 @@
         <v>13</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J41" s="6">
         <v>43840</v>
@@ -2177,13 +2181,13 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>58</v>
+      <c r="E42" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>158</v>
@@ -2206,8 +2210,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2215,7 +2219,7 @@
         <v>60</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G43" s="6">
         <v>43828</v>
@@ -2223,18 +2227,22 @@
       <c r="H43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
+      <c r="I43" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="J43" s="6">
+        <v>43841</v>
+      </c>
       <c r="K43" s="5"/>
     </row>
     <row r="44" spans="1:11" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="17" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2260,8 +2268,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2285,8 +2293,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2310,8 +2318,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2335,8 +2343,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="19"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2360,7 +2368,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="12"/>
+      <c r="B49" s="19"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2387,10 +2395,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2416,8 +2424,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2441,8 +2449,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2466,8 +2474,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2491,8 +2499,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="19"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2516,7 +2524,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="12"/>
+      <c r="B55" s="19"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2543,10 +2551,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2572,8 +2580,8 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
       <c r="D57" s="7" t="s">
         <v>93</v>
       </c>
@@ -2597,8 +2605,8 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
       <c r="D58" s="7" t="s">
         <v>95</v>
       </c>
@@ -2622,8 +2630,8 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
       <c r="D59" s="5" t="s">
         <v>97</v>
       </c>
@@ -2647,8 +2655,8 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="11"/>
-      <c r="C60" s="12"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="19"/>
       <c r="D60" s="5" t="s">
         <v>99</v>
       </c>
@@ -2672,7 +2680,7 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="12"/>
+      <c r="B61" s="19"/>
       <c r="C61" s="5" t="s">
         <v>100</v>
       </c>
@@ -2699,10 +2707,10 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="17" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2728,8 +2736,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
       <c r="D63" s="5" t="s">
         <v>105</v>
       </c>
@@ -2753,8 +2761,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
       <c r="D64" s="5" t="s">
         <v>106</v>
       </c>
@@ -2778,8 +2786,8 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
       <c r="D65" s="5" t="s">
         <v>107</v>
       </c>
@@ -2803,8 +2811,8 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="19"/>
       <c r="D66" s="5" t="s">
         <v>109</v>
       </c>
@@ -2828,7 +2836,7 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="12"/>
+      <c r="B67" s="19"/>
       <c r="C67" s="5" t="s">
         <v>110</v>
       </c>
@@ -2855,10 +2863,10 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="17" t="s">
         <v>113</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -2884,8 +2892,8 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
       <c r="D69" s="5" t="s">
         <v>115</v>
       </c>
@@ -2909,8 +2917,8 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
       <c r="D70" s="5" t="s">
         <v>117</v>
       </c>
@@ -2934,8 +2942,8 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
       <c r="D71" s="5" t="s">
         <v>118</v>
       </c>
@@ -2959,8 +2967,8 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="12"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="19"/>
       <c r="D72" s="5" t="s">
         <v>120</v>
       </c>
@@ -2984,7 +2992,7 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="12"/>
+      <c r="B73" s="19"/>
       <c r="C73" s="5" t="s">
         <v>121</v>
       </c>
@@ -3011,10 +3019,10 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C74" s="17" t="s">
         <v>124</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -3040,8 +3048,8 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
       <c r="D75" s="5" t="s">
         <v>126</v>
       </c>
@@ -3065,8 +3073,8 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
       <c r="D76" s="5" t="s">
         <v>127</v>
       </c>
@@ -3090,8 +3098,8 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
       <c r="D77" s="5" t="s">
         <v>128</v>
       </c>
@@ -3115,8 +3123,8 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="11"/>
-      <c r="C78" s="12"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="19"/>
       <c r="D78" s="5" t="s">
         <v>130</v>
       </c>
@@ -3140,7 +3148,7 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="12"/>
+      <c r="B79" s="19"/>
       <c r="C79" s="5" t="s">
         <v>131</v>
       </c>
@@ -3167,10 +3175,10 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="17" t="s">
         <v>134</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -3196,8 +3204,8 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
       <c r="D81" s="5" t="s">
         <v>136</v>
       </c>
@@ -3221,8 +3229,8 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
       <c r="D82" s="5" t="s">
         <v>138</v>
       </c>
@@ -3246,8 +3254,8 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
       <c r="D83" s="5" t="s">
         <v>139</v>
       </c>
@@ -3271,8 +3279,8 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="11"/>
-      <c r="C84" s="12"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="19"/>
       <c r="D84" s="5" t="s">
         <v>141</v>
       </c>
@@ -3296,7 +3304,7 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="12"/>
+      <c r="B85" s="19"/>
       <c r="C85" s="5" t="s">
         <v>142</v>
       </c>
@@ -3323,10 +3331,10 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" s="17" t="s">
         <v>145</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -3352,8 +3360,8 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
       <c r="D87" s="5" t="s">
         <v>147</v>
       </c>
@@ -3377,8 +3385,8 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
       <c r="D88" s="5" t="s">
         <v>148</v>
       </c>
@@ -3402,8 +3410,8 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
       <c r="D89" s="5" t="s">
         <v>149</v>
       </c>
@@ -3427,8 +3435,8 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="11"/>
-      <c r="C90" s="12"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="19"/>
       <c r="D90" s="5" t="s">
         <v>151</v>
       </c>
@@ -3452,7 +3460,7 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="12"/>
+      <c r="B91" s="19"/>
       <c r="C91" s="5" t="s">
         <v>152</v>
       </c>
@@ -3476,15 +3484,15 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="18"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="15"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3499,19 +3507,19 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="17" t="s">
+      <c r="A97" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="19"/>
-      <c r="K97" s="19"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="16"/>
+      <c r="J97" s="16"/>
+      <c r="K97" s="16"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
@@ -3550,6 +3558,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A92:G92"/>
@@ -3566,15 +3583,6 @@
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5C4694-3CBC-4523-A895-9060AB8EB4E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3543CCC5-E9E6-4F0C-BFE0-367F1F90CDA7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2805" yWindow="2070" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="167">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -528,6 +528,10 @@
   </si>
   <si>
     <t>凌家童</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -700,7 +704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -727,6 +731,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -760,6 +767,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1203,19 +1213,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1671,19 +1681,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1724,7 +1734,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1757,7 +1767,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="18"/>
+      <c r="B28" s="19"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1790,7 +1800,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="18"/>
+      <c r="B29" s="19"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1823,7 +1833,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="18"/>
+      <c r="B30" s="19"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1856,7 +1866,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="19"/>
+      <c r="B31" s="20"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1885,10 +1895,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1918,8 +1928,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -1947,8 +1957,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -1976,8 +1986,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -2001,8 +2011,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="20"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2026,7 +2036,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="18"/>
+      <c r="B37" s="19"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2057,10 +2067,10 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="21" t="s">
         <v>162</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -2090,8 +2100,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2119,8 +2129,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2150,8 +2160,8 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
@@ -2181,8 +2191,8 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
@@ -2210,8 +2220,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2239,10 +2249,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="18" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2268,8 +2278,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2293,8 +2303,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2318,8 +2328,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2343,8 +2353,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="18"/>
-      <c r="C48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="20"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2368,7 +2378,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="19"/>
+      <c r="B49" s="20"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2395,10 +2405,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2424,8 +2434,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2449,8 +2459,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2474,8 +2484,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2499,8 +2509,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="19"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="20"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2524,7 +2534,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="19"/>
+      <c r="B55" s="20"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2551,10 +2561,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="18" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2563,8 +2573,8 @@
       <c r="E56" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>12</v>
+      <c r="F56" s="9" t="s">
+        <v>166</v>
       </c>
       <c r="G56" s="6">
         <v>43828</v>
@@ -2572,24 +2582,28 @@
       <c r="H56" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
+      <c r="I56" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="J56" s="6">
+        <v>43841</v>
+      </c>
       <c r="K56" s="5"/>
     </row>
     <row r="57" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
       <c r="D57" s="7" t="s">
         <v>93</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>12</v>
+      <c r="F57" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G57" s="6">
         <v>43828</v>
@@ -2597,24 +2611,28 @@
       <c r="H57" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="I57" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="J57" s="22">
+        <v>43841</v>
+      </c>
       <c r="K57" s="7"/>
     </row>
     <row r="58" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
       <c r="D58" s="7" t="s">
         <v>95</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>12</v>
+      <c r="F58" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G58" s="6">
         <v>43828</v>
@@ -2622,24 +2640,28 @@
       <c r="H58" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="I58" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="J58" s="22">
+        <v>43841</v>
+      </c>
       <c r="K58" s="7"/>
     </row>
     <row r="59" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
       <c r="D59" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>12</v>
+      <c r="F59" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G59" s="6">
         <v>43828</v>
@@ -2647,24 +2669,28 @@
       <c r="H59" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
+      <c r="I59" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="J59" s="22">
+        <v>43841</v>
+      </c>
       <c r="K59" s="5"/>
     </row>
     <row r="60" spans="1:11" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="19"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="20"/>
       <c r="D60" s="5" t="s">
         <v>99</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>12</v>
+      <c r="F60" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G60" s="6">
         <v>43828</v>
@@ -2672,15 +2698,19 @@
       <c r="H60" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+      <c r="I60" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="J60" s="22">
+        <v>43841</v>
+      </c>
       <c r="K60" s="5"/>
     </row>
     <row r="61" spans="1:11" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="19"/>
+      <c r="B61" s="20"/>
       <c r="C61" s="5" t="s">
         <v>100</v>
       </c>
@@ -2690,8 +2720,8 @@
       <c r="E61" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F61" s="5" t="s">
-        <v>12</v>
+      <c r="F61" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="G61" s="6">
         <v>43828</v>
@@ -2699,18 +2729,22 @@
       <c r="H61" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+      <c r="I61" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="J61" s="22">
+        <v>43841</v>
+      </c>
       <c r="K61" s="5"/>
     </row>
     <row r="62" spans="1:11" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="18" t="s">
         <v>103</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2736,8 +2770,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
       <c r="D63" s="5" t="s">
         <v>105</v>
       </c>
@@ -2761,8 +2795,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
       <c r="D64" s="5" t="s">
         <v>106</v>
       </c>
@@ -2786,8 +2820,8 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
       <c r="D65" s="5" t="s">
         <v>107</v>
       </c>
@@ -2811,8 +2845,8 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="19"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="20"/>
       <c r="D66" s="5" t="s">
         <v>109</v>
       </c>
@@ -2836,7 +2870,7 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="19"/>
+      <c r="B67" s="20"/>
       <c r="C67" s="5" t="s">
         <v>110</v>
       </c>
@@ -2863,10 +2897,10 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="18" t="s">
         <v>113</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -2892,8 +2926,8 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
       <c r="D69" s="5" t="s">
         <v>115</v>
       </c>
@@ -2917,8 +2951,8 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="18"/>
-      <c r="C70" s="18"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
       <c r="D70" s="5" t="s">
         <v>117</v>
       </c>
@@ -2942,8 +2976,8 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
       <c r="D71" s="5" t="s">
         <v>118</v>
       </c>
@@ -2967,8 +3001,8 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="18"/>
-      <c r="C72" s="19"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="20"/>
       <c r="D72" s="5" t="s">
         <v>120</v>
       </c>
@@ -2992,7 +3026,7 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="19"/>
+      <c r="B73" s="20"/>
       <c r="C73" s="5" t="s">
         <v>121</v>
       </c>
@@ -3019,10 +3053,10 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="18" t="s">
         <v>124</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -3048,8 +3082,8 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
       <c r="D75" s="5" t="s">
         <v>126</v>
       </c>
@@ -3073,8 +3107,8 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
       <c r="D76" s="5" t="s">
         <v>127</v>
       </c>
@@ -3098,8 +3132,8 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
       <c r="D77" s="5" t="s">
         <v>128</v>
       </c>
@@ -3123,8 +3157,8 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="18"/>
-      <c r="C78" s="19"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="20"/>
       <c r="D78" s="5" t="s">
         <v>130</v>
       </c>
@@ -3148,7 +3182,7 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="19"/>
+      <c r="B79" s="20"/>
       <c r="C79" s="5" t="s">
         <v>131</v>
       </c>
@@ -3175,10 +3209,10 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B80" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="18" t="s">
         <v>134</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -3204,8 +3238,8 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
       <c r="D81" s="5" t="s">
         <v>136</v>
       </c>
@@ -3229,8 +3263,8 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
       <c r="D82" s="5" t="s">
         <v>138</v>
       </c>
@@ -3254,8 +3288,8 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
       <c r="D83" s="5" t="s">
         <v>139</v>
       </c>
@@ -3279,8 +3313,8 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="18"/>
-      <c r="C84" s="19"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="20"/>
       <c r="D84" s="5" t="s">
         <v>141</v>
       </c>
@@ -3304,7 +3338,7 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="19"/>
+      <c r="B85" s="20"/>
       <c r="C85" s="5" t="s">
         <v>142</v>
       </c>
@@ -3331,10 +3365,10 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B86" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="18" t="s">
         <v>145</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -3360,8 +3394,8 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="19"/>
       <c r="D87" s="5" t="s">
         <v>147</v>
       </c>
@@ -3385,8 +3419,8 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="19"/>
       <c r="D88" s="5" t="s">
         <v>148</v>
       </c>
@@ -3410,8 +3444,8 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
       <c r="D89" s="5" t="s">
         <v>149</v>
       </c>
@@ -3435,8 +3469,8 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="18"/>
-      <c r="C90" s="19"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="20"/>
       <c r="D90" s="5" t="s">
         <v>151</v>
       </c>
@@ -3460,7 +3494,7 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="19"/>
+      <c r="B91" s="20"/>
       <c r="C91" s="5" t="s">
         <v>152</v>
       </c>
@@ -3484,15 +3518,15 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3507,19 +3541,19 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
-      <c r="E97" s="16"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="16"/>
-      <c r="H97" s="16"/>
-      <c r="I97" s="16"/>
-      <c r="J97" s="16"/>
-      <c r="K97" s="16"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="17"/>
+      <c r="F97" s="17"/>
+      <c r="G97" s="17"/>
+      <c r="H97" s="17"/>
+      <c r="I97" s="17"/>
+      <c r="J97" s="17"/>
+      <c r="K97" s="17"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22325"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3543CCC5-E9E6-4F0C-BFE0-367F1F90CDA7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237CE831-EA56-4463-82D4-F59B055691B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="2070" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="168">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -299,12 +299,6 @@
   </si>
   <si>
     <t>表格形式显示链接列表，表格上面有查询表单，表单按照name、type属性进行查询条件拼接，其中type为下拉列表</t>
-  </si>
-  <si>
-    <t>根据name、type字段查询链接</t>
-  </si>
-  <si>
-    <t>其中name为模糊查询、type为下拉列表</t>
   </si>
   <si>
     <t>删除链接</t>
@@ -528,6 +522,18 @@
   </si>
   <si>
     <t>凌家童</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name、type、url字段查询链接</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>其中name、url为模糊查询、type为下拉列表</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -704,7 +710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -736,6 +742,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -755,21 +779,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1213,19 +1222,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1681,19 +1690,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1734,7 +1743,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1767,7 +1776,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="19"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1800,7 +1809,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="19"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1833,7 +1842,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="19"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1866,7 +1875,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="20"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1895,10 +1904,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="13" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1928,8 +1937,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -1957,8 +1966,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -1986,8 +1995,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -1995,7 +2004,7 @@
         <v>41</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G35" s="6">
         <v>43828</v>
@@ -2011,8 +2020,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="20"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="15"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2020,7 +2029,7 @@
         <v>43</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G36" s="6">
         <v>43828</v>
@@ -2036,7 +2045,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="19"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2047,7 +2056,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G37" s="6">
         <v>43828</v>
@@ -2056,7 +2065,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J37" s="6">
         <v>43840</v>
@@ -2067,11 +2076,11 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="21" t="s">
-        <v>162</v>
+      <c r="C38" s="16" t="s">
+        <v>160</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>48</v>
@@ -2080,7 +2089,7 @@
         <v>49</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G38" s="6">
         <v>43828</v>
@@ -2089,7 +2098,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J38" s="6">
         <v>43840</v>
@@ -2100,8 +2109,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2109,7 +2118,7 @@
         <v>51</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G39" s="6">
         <v>43828</v>
@@ -2118,7 +2127,7 @@
         <v>13</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J39" s="6">
         <v>43839</v>
@@ -2129,8 +2138,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2138,7 +2147,7 @@
         <v>53</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G40" s="6">
         <v>43828</v>
@@ -2147,7 +2156,7 @@
         <v>13</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J40" s="6">
         <v>43839</v>
@@ -2160,16 +2169,16 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G41" s="6">
         <v>43828</v>
@@ -2178,7 +2187,7 @@
         <v>13</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J41" s="6">
         <v>43840</v>
@@ -2191,16 +2200,16 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G42" s="6">
         <v>43828</v>
@@ -2209,7 +2218,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J42" s="6">
         <v>43839</v>
@@ -2220,8 +2229,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2229,7 +2238,7 @@
         <v>60</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G43" s="6">
         <v>43828</v>
@@ -2238,7 +2247,7 @@
         <v>13</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J43" s="6">
         <v>43841</v>
@@ -2249,10 +2258,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2278,8 +2287,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2303,8 +2312,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2328,8 +2337,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2353,8 +2362,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="20"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="15"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2378,7 +2387,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="20"/>
+      <c r="B49" s="15"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2405,10 +2414,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="13" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2434,8 +2443,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2459,8 +2468,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2484,8 +2493,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2509,8 +2518,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="20"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="15"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2534,7 +2543,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="20"/>
+      <c r="B55" s="15"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2561,10 +2570,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="13" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2574,7 +2583,7 @@
         <v>92</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G56" s="6">
         <v>43828</v>
@@ -2583,7 +2592,7 @@
         <v>13</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J56" s="6">
         <v>43841</v>
@@ -2594,16 +2603,16 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>94</v>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>166</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G57" s="6">
         <v>43828</v>
@@ -2612,9 +2621,9 @@
         <v>13</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J57" s="22">
+        <v>163</v>
+      </c>
+      <c r="J57" s="12">
         <v>43841</v>
       </c>
       <c r="K57" s="7"/>
@@ -2623,16 +2632,16 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
       <c r="D58" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G58" s="6">
         <v>43828</v>
@@ -2641,9 +2650,9 @@
         <v>13</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J58" s="22">
+        <v>163</v>
+      </c>
+      <c r="J58" s="12">
         <v>43841</v>
       </c>
       <c r="K58" s="7"/>
@@ -2652,16 +2661,16 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
       <c r="D59" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G59" s="6">
         <v>43828</v>
@@ -2670,9 +2679,9 @@
         <v>13</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J59" s="22">
+        <v>163</v>
+      </c>
+      <c r="J59" s="12">
         <v>43841</v>
       </c>
       <c r="K59" s="5"/>
@@ -2681,16 +2690,16 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="20"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="15"/>
       <c r="D60" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G60" s="6">
         <v>43828</v>
@@ -2699,9 +2708,9 @@
         <v>13</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J60" s="22">
+        <v>163</v>
+      </c>
+      <c r="J60" s="12">
         <v>43841</v>
       </c>
       <c r="K60" s="5"/>
@@ -2710,18 +2719,18 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="20"/>
+      <c r="B61" s="15"/>
       <c r="C61" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G61" s="6">
         <v>43828</v>
@@ -2730,9 +2739,9 @@
         <v>13</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J61" s="22">
+        <v>163</v>
+      </c>
+      <c r="J61" s="12">
         <v>43841</v>
       </c>
       <c r="K61" s="5"/>
@@ -2741,20 +2750,20 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>12</v>
+      <c r="F62" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="G62" s="6">
         <v>43828</v>
@@ -2762,24 +2771,28 @@
       <c r="H62" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
+      <c r="I62" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="J62" s="12">
+        <v>43843</v>
+      </c>
       <c r="K62" s="5"/>
     </row>
     <row r="63" spans="1:11" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
       <c r="D63" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>12</v>
+        <v>103</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="G63" s="6">
         <v>43828</v>
@@ -2787,24 +2800,28 @@
       <c r="H63" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
+      <c r="I63" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="J63" s="12">
+        <v>43843</v>
+      </c>
       <c r="K63" s="5"/>
     </row>
     <row r="64" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
       <c r="D64" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>12</v>
+        <v>94</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="G64" s="6">
         <v>43828</v>
@@ -2812,24 +2829,28 @@
       <c r="H64" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
+      <c r="I64" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="J64" s="12">
+        <v>43843</v>
+      </c>
       <c r="K64" s="5"/>
     </row>
     <row r="65" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
       <c r="D65" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>12</v>
+        <v>106</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="G65" s="6">
         <v>43828</v>
@@ -2837,24 +2858,28 @@
       <c r="H65" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
+      <c r="I65" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="J65" s="12">
+        <v>43843</v>
+      </c>
       <c r="K65" s="5"/>
     </row>
     <row r="66" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="19"/>
-      <c r="C66" s="20"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="15"/>
       <c r="D66" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>12</v>
+      <c r="F66" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="G66" s="6">
         <v>43828</v>
@@ -2862,26 +2887,30 @@
       <c r="H66" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
+      <c r="I66" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="J66" s="12">
+        <v>43843</v>
+      </c>
       <c r="K66" s="5"/>
     </row>
     <row r="67" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="20"/>
+      <c r="B67" s="15"/>
       <c r="C67" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>12</v>
+        <v>109</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="G67" s="6">
         <v>43828</v>
@@ -2889,25 +2918,29 @@
       <c r="H67" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
+      <c r="I67" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="J67" s="12">
+        <v>43843</v>
+      </c>
       <c r="K67" s="5"/>
     </row>
     <row r="68" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>12</v>
@@ -2926,13 +2959,13 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
       <c r="D69" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>12</v>
@@ -2951,13 +2984,13 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
       <c r="D70" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>12</v>
@@ -2976,13 +3009,13 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
       <c r="D71" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>12</v>
@@ -3001,10 +3034,10 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="20"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="15"/>
       <c r="D72" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>58</v>
@@ -3026,15 +3059,15 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="20"/>
+      <c r="B73" s="15"/>
       <c r="C73" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>12</v>
@@ -3053,17 +3086,17 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C74" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>12</v>
@@ -3082,13 +3115,13 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
       <c r="D75" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>12</v>
@@ -3107,13 +3140,13 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
       <c r="D76" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>12</v>
@@ -3132,13 +3165,13 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
       <c r="D77" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>12</v>
@@ -3157,10 +3190,10 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="19"/>
-      <c r="C78" s="20"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="15"/>
       <c r="D78" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>58</v>
@@ -3182,15 +3215,15 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="20"/>
+      <c r="B79" s="15"/>
       <c r="C79" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>12</v>
@@ -3209,17 +3242,17 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="B80" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>12</v>
@@ -3238,13 +3271,13 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
       <c r="D81" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>12</v>
@@ -3263,13 +3296,13 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
       <c r="D82" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>12</v>
@@ -3288,13 +3321,13 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
       <c r="D83" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>12</v>
@@ -3313,10 +3346,10 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="20"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="15"/>
       <c r="D84" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>58</v>
@@ -3338,15 +3371,15 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="20"/>
+      <c r="B85" s="15"/>
       <c r="C85" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>12</v>
@@ -3365,17 +3398,17 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>12</v>
@@ -3394,13 +3427,13 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
       <c r="D87" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>12</v>
@@ -3419,13 +3452,13 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
       <c r="D88" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>12</v>
@@ -3444,13 +3477,13 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
       <c r="D89" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>12</v>
@@ -3469,10 +3502,10 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="19"/>
-      <c r="C90" s="20"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="15"/>
       <c r="D90" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>58</v>
@@ -3494,15 +3527,15 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="20"/>
+      <c r="B91" s="15"/>
       <c r="C91" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>12</v>
@@ -3518,15 +3551,15 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
+      <c r="A92" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3541,23 +3574,23 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="17"/>
-      <c r="G97" s="17"/>
-      <c r="H97" s="17"/>
-      <c r="I97" s="17"/>
-      <c r="J97" s="17"/>
-      <c r="K97" s="17"/>
+      <c r="A97" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97" s="23"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
+      <c r="G97" s="23"/>
+      <c r="H97" s="23"/>
+      <c r="I97" s="23"/>
+      <c r="J97" s="23"/>
+      <c r="K97" s="23"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>2</v>
@@ -3592,15 +3625,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A92:G92"/>
@@ -3617,6 +3641,15 @@
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237CE831-EA56-4463-82D4-F59B055691B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D748EA-3E88-4CF0-973C-6268EE781D70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="170">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -338,9 +338,6 @@
   </si>
   <si>
     <t>编辑链接类型</t>
-  </si>
-  <si>
-    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性只有name</t>
   </si>
   <si>
     <t>恢复链接类型</t>
@@ -538,6 +535,18 @@
   </si>
   <si>
     <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性只有name</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌家童</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -748,18 +757,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -779,6 +776,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1222,19 +1231,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1690,19 +1699,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1743,7 +1752,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1776,7 +1785,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="14"/>
+      <c r="B28" s="21"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1809,7 +1818,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="14"/>
+      <c r="B29" s="21"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1842,7 +1851,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="14"/>
+      <c r="B30" s="21"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1875,7 +1884,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="15"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1904,10 +1913,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1937,8 +1946,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -1966,8 +1975,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -1995,8 +2004,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -2004,7 +2013,7 @@
         <v>41</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G35" s="6">
         <v>43828</v>
@@ -2020,8 +2029,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="15"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2029,7 +2038,7 @@
         <v>43</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G36" s="6">
         <v>43828</v>
@@ -2045,7 +2054,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="14"/>
+      <c r="B37" s="21"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2056,7 +2065,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G37" s="6">
         <v>43828</v>
@@ -2065,7 +2074,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J37" s="6">
         <v>43840</v>
@@ -2076,11 +2085,11 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>160</v>
+      <c r="C38" s="23" t="s">
+        <v>159</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>48</v>
@@ -2089,7 +2098,7 @@
         <v>49</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G38" s="6">
         <v>43828</v>
@@ -2098,7 +2107,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J38" s="6">
         <v>43840</v>
@@ -2109,8 +2118,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2118,16 +2127,16 @@
         <v>51</v>
       </c>
       <c r="F39" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G39" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="G39" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="J39" s="6">
         <v>43839</v>
@@ -2138,8 +2147,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2147,16 +2156,16 @@
         <v>53</v>
       </c>
       <c r="F40" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G40" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="G40" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="J40" s="6">
         <v>43839</v>
@@ -2169,25 +2178,25 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G41" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G41" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="J41" s="6">
         <v>43840</v>
@@ -2200,25 +2209,25 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F42" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="G42" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="J42" s="6">
         <v>43839</v>
@@ -2229,8 +2238,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2238,7 +2247,7 @@
         <v>60</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G43" s="6">
         <v>43828</v>
@@ -2247,7 +2256,7 @@
         <v>13</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J43" s="6">
         <v>43841</v>
@@ -2258,10 +2267,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2287,8 +2296,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2312,8 +2321,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2337,8 +2346,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2362,8 +2371,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="15"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="22"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2387,7 +2396,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="15"/>
+      <c r="B49" s="22"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2414,10 +2423,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="20" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2443,8 +2452,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2468,8 +2477,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2493,8 +2502,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2518,8 +2527,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="15"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="22"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2543,7 +2552,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="15"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2570,10 +2579,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="20" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2583,7 +2592,7 @@
         <v>92</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G56" s="6">
         <v>43828</v>
@@ -2592,7 +2601,7 @@
         <v>13</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J56" s="6">
         <v>43841</v>
@@ -2603,16 +2612,16 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
       <c r="D57" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E57" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E57" s="11" t="s">
-        <v>166</v>
-      </c>
       <c r="F57" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G57" s="6">
         <v>43828</v>
@@ -2621,7 +2630,7 @@
         <v>13</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J57" s="12">
         <v>43841</v>
@@ -2632,8 +2641,8 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
       <c r="D58" s="7" t="s">
         <v>93</v>
       </c>
@@ -2641,7 +2650,7 @@
         <v>94</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G58" s="6">
         <v>43828</v>
@@ -2650,7 +2659,7 @@
         <v>13</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J58" s="12">
         <v>43841</v>
@@ -2661,8 +2670,8 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
       <c r="D59" s="5" t="s">
         <v>95</v>
       </c>
@@ -2670,7 +2679,7 @@
         <v>96</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G59" s="6">
         <v>43828</v>
@@ -2679,7 +2688,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J59" s="12">
         <v>43841</v>
@@ -2690,8 +2699,8 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="15"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="22"/>
       <c r="D60" s="5" t="s">
         <v>97</v>
       </c>
@@ -2699,7 +2708,7 @@
         <v>58</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G60" s="6">
         <v>43828</v>
@@ -2708,7 +2717,7 @@
         <v>13</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J60" s="12">
         <v>43841</v>
@@ -2719,7 +2728,7 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="15"/>
+      <c r="B61" s="22"/>
       <c r="C61" s="5" t="s">
         <v>98</v>
       </c>
@@ -2730,7 +2739,7 @@
         <v>99</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G61" s="6">
         <v>43828</v>
@@ -2739,7 +2748,7 @@
         <v>13</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J61" s="12">
         <v>43841</v>
@@ -2750,10 +2759,10 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="20" t="s">
         <v>101</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2763,7 +2772,7 @@
         <v>102</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G62" s="6">
         <v>43828</v>
@@ -2772,7 +2781,7 @@
         <v>13</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J62" s="12">
         <v>43843</v>
@@ -2783,8 +2792,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21"/>
       <c r="D63" s="5" t="s">
         <v>103</v>
       </c>
@@ -2792,7 +2801,7 @@
         <v>103</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G63" s="6">
         <v>43828</v>
@@ -2801,7 +2810,7 @@
         <v>13</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J63" s="12">
         <v>43843</v>
@@ -2812,8 +2821,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
       <c r="D64" s="5" t="s">
         <v>104</v>
       </c>
@@ -2821,7 +2830,7 @@
         <v>94</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G64" s="6">
         <v>43828</v>
@@ -2830,7 +2839,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J64" s="12">
         <v>43843</v>
@@ -2841,16 +2850,16 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="21"/>
       <c r="D65" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>106</v>
+      <c r="E65" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G65" s="6">
         <v>43828</v>
@@ -2859,7 +2868,7 @@
         <v>13</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J65" s="12">
         <v>43843</v>
@@ -2870,16 +2879,16 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="15"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="22"/>
       <c r="D66" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G66" s="6">
         <v>43828</v>
@@ -2888,7 +2897,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J66" s="12">
         <v>43843</v>
@@ -2899,18 +2908,18 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="15"/>
+      <c r="B67" s="22"/>
       <c r="C67" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="F67" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G67" s="6">
         <v>43828</v>
@@ -2919,7 +2928,7 @@
         <v>13</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J67" s="12">
         <v>43843</v>
@@ -2930,17 +2939,17 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="D68" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>12</v>
@@ -2959,13 +2968,13 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
       <c r="D69" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>12</v>
@@ -2984,10 +2993,10 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
       <c r="D70" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>94</v>
@@ -3009,13 +3018,13 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
       <c r="D71" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>12</v>
@@ -3034,10 +3043,10 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="15"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="22"/>
       <c r="D72" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>58</v>
@@ -3059,15 +3068,15 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="15"/>
+      <c r="B73" s="22"/>
       <c r="C73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>12</v>
@@ -3086,20 +3095,20 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C74" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="D74" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>12</v>
+      <c r="F74" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G74" s="6">
         <v>43828</v>
@@ -3107,24 +3116,28 @@
       <c r="H74" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
+      <c r="I74" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J74" s="6">
+        <v>43844</v>
+      </c>
       <c r="K74" s="5"/>
     </row>
     <row r="75" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
       <c r="D75" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>12</v>
+        <v>123</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G75" s="6">
         <v>43828</v>
@@ -3132,24 +3145,28 @@
       <c r="H75" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
+      <c r="I75" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J75" s="6">
+        <v>43844</v>
+      </c>
       <c r="K75" s="5"/>
     </row>
     <row r="76" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
       <c r="D76" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F76" s="5" t="s">
-        <v>12</v>
+      <c r="F76" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G76" s="6">
         <v>43828</v>
@@ -3157,24 +3174,28 @@
       <c r="H76" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
+      <c r="I76" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J76" s="6">
+        <v>43844</v>
+      </c>
       <c r="K76" s="5"/>
     </row>
     <row r="77" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="21"/>
       <c r="D77" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>12</v>
+      <c r="F77" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G77" s="6">
         <v>43828</v>
@@ -3182,24 +3203,28 @@
       <c r="H77" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
+      <c r="I77" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J77" s="6">
+        <v>43844</v>
+      </c>
       <c r="K77" s="5"/>
     </row>
     <row r="78" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="14"/>
-      <c r="C78" s="15"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="22"/>
       <c r="D78" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F78" s="5" t="s">
-        <v>12</v>
+      <c r="F78" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G78" s="6">
         <v>43828</v>
@@ -3207,26 +3232,30 @@
       <c r="H78" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
+      <c r="I78" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J78" s="6">
+        <v>43844</v>
+      </c>
       <c r="K78" s="5"/>
     </row>
     <row r="79" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="15"/>
+      <c r="B79" s="22"/>
       <c r="C79" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D79" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>12</v>
+      <c r="F79" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="G79" s="6">
         <v>43828</v>
@@ -3234,25 +3263,29 @@
       <c r="H79" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
+      <c r="I79" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J79" s="6">
+        <v>43844</v>
+      </c>
       <c r="K79" s="5"/>
     </row>
     <row r="80" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="D80" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>12</v>
@@ -3271,13 +3304,13 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
+      <c r="B81" s="21"/>
+      <c r="C81" s="21"/>
       <c r="D81" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>12</v>
@@ -3296,10 +3329,10 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="21"/>
       <c r="D82" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>94</v>
@@ -3321,13 +3354,13 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="21"/>
       <c r="D83" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>12</v>
@@ -3346,10 +3379,10 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="15"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="22"/>
       <c r="D84" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>58</v>
@@ -3371,15 +3404,15 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="15"/>
+      <c r="B85" s="22"/>
       <c r="C85" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>12</v>
@@ -3398,17 +3431,17 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C86" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="D86" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>12</v>
@@ -3427,13 +3460,13 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
       <c r="D87" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>12</v>
@@ -3452,10 +3485,10 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14"/>
+      <c r="B88" s="21"/>
+      <c r="C88" s="21"/>
       <c r="D88" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>94</v>
@@ -3477,13 +3510,13 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="14"/>
-      <c r="C89" s="14"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="21"/>
       <c r="D89" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>12</v>
@@ -3502,10 +3535,10 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="14"/>
-      <c r="C90" s="15"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="22"/>
       <c r="D90" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>58</v>
@@ -3527,15 +3560,15 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="15"/>
+      <c r="B91" s="22"/>
       <c r="C91" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>12</v>
@@ -3551,15 +3584,15 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B92" s="22"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="22"/>
-      <c r="F92" s="22"/>
-      <c r="G92" s="22"/>
+      <c r="A92" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3574,23 +3607,23 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B97" s="23"/>
-      <c r="C97" s="23"/>
-      <c r="D97" s="23"/>
-      <c r="E97" s="23"/>
-      <c r="F97" s="23"/>
-      <c r="G97" s="23"/>
-      <c r="H97" s="23"/>
-      <c r="I97" s="23"/>
-      <c r="J97" s="23"/>
-      <c r="K97" s="23"/>
+      <c r="A97" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="19"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="19"/>
+      <c r="I97" s="19"/>
+      <c r="J97" s="19"/>
+      <c r="K97" s="19"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>2</v>
@@ -3625,6 +3658,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A92:G92"/>
@@ -3641,15 +3683,6 @@
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D748EA-3E88-4CF0-973C-6268EE781D70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9B1048-7289-4CD4-A8EA-2D7457C68501}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-195" yWindow="1110" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="171">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -389,9 +389,6 @@
   </si>
   <si>
     <t>表格形式显示技能列表，表格上面有查询表单，通过name、owner、precent字段模糊查询</t>
-  </si>
-  <si>
-    <t>根据name、owner、precent字段模糊查询</t>
   </si>
   <si>
     <t>删除技能</t>
@@ -547,6 +544,14 @@
   </si>
   <si>
     <t>凌家童</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据name、owner字段模糊查询</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2013,7 +2018,7 @@
         <v>41</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G35" s="6">
         <v>43828</v>
@@ -2038,7 +2043,7 @@
         <v>43</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G36" s="6">
         <v>43828</v>
@@ -2065,7 +2070,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G37" s="6">
         <v>43828</v>
@@ -2074,7 +2079,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J37" s="6">
         <v>43840</v>
@@ -2089,7 +2094,7 @@
         <v>47</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>48</v>
@@ -2098,7 +2103,7 @@
         <v>49</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G38" s="6">
         <v>43828</v>
@@ -2107,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J38" s="6">
         <v>43840</v>
@@ -2127,16 +2132,16 @@
         <v>51</v>
       </c>
       <c r="F39" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="G39" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="G39" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="J39" s="6">
         <v>43839</v>
@@ -2156,16 +2161,16 @@
         <v>53</v>
       </c>
       <c r="F40" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="G40" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="G40" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="J40" s="6">
         <v>43839</v>
@@ -2184,19 +2189,19 @@
         <v>55</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G41" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G41" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="J41" s="6">
         <v>43840</v>
@@ -2215,19 +2220,19 @@
         <v>57</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F42" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="G42" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>155</v>
-      </c>
-      <c r="G42" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>156</v>
       </c>
       <c r="J42" s="6">
         <v>43839</v>
@@ -2247,7 +2252,7 @@
         <v>60</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G43" s="6">
         <v>43828</v>
@@ -2256,7 +2261,7 @@
         <v>13</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J43" s="6">
         <v>43841</v>
@@ -2592,7 +2597,7 @@
         <v>92</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G56" s="6">
         <v>43828</v>
@@ -2601,7 +2606,7 @@
         <v>13</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J56" s="6">
         <v>43841</v>
@@ -2615,13 +2620,13 @@
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E57" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E57" s="11" t="s">
-        <v>165</v>
-      </c>
       <c r="F57" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G57" s="6">
         <v>43828</v>
@@ -2630,7 +2635,7 @@
         <v>13</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J57" s="12">
         <v>43841</v>
@@ -2650,7 +2655,7 @@
         <v>94</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G58" s="6">
         <v>43828</v>
@@ -2659,7 +2664,7 @@
         <v>13</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J58" s="12">
         <v>43841</v>
@@ -2679,7 +2684,7 @@
         <v>96</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G59" s="6">
         <v>43828</v>
@@ -2688,7 +2693,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J59" s="12">
         <v>43841</v>
@@ -2708,7 +2713,7 @@
         <v>58</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G60" s="6">
         <v>43828</v>
@@ -2717,7 +2722,7 @@
         <v>13</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J60" s="12">
         <v>43841</v>
@@ -2739,7 +2744,7 @@
         <v>99</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G61" s="6">
         <v>43828</v>
@@ -2748,7 +2753,7 @@
         <v>13</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J61" s="12">
         <v>43841</v>
@@ -2772,7 +2777,7 @@
         <v>102</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G62" s="6">
         <v>43828</v>
@@ -2781,7 +2786,7 @@
         <v>13</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J62" s="12">
         <v>43843</v>
@@ -2801,7 +2806,7 @@
         <v>103</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G63" s="6">
         <v>43828</v>
@@ -2810,7 +2815,7 @@
         <v>13</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J63" s="12">
         <v>43843</v>
@@ -2830,7 +2835,7 @@
         <v>94</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G64" s="6">
         <v>43828</v>
@@ -2839,7 +2844,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J64" s="12">
         <v>43843</v>
@@ -2856,10 +2861,10 @@
         <v>105</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G65" s="6">
         <v>43828</v>
@@ -2868,7 +2873,7 @@
         <v>13</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J65" s="12">
         <v>43843</v>
@@ -2888,7 +2893,7 @@
         <v>58</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G66" s="6">
         <v>43828</v>
@@ -2897,7 +2902,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J66" s="12">
         <v>43843</v>
@@ -2919,7 +2924,7 @@
         <v>108</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G67" s="6">
         <v>43828</v>
@@ -2928,7 +2933,7 @@
         <v>13</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J67" s="12">
         <v>43843</v>
@@ -3108,16 +3113,16 @@
         <v>122</v>
       </c>
       <c r="F74" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G74" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G74" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J74" s="6">
         <v>43844</v>
@@ -3130,23 +3135,23 @@
       </c>
       <c r="B75" s="21"/>
       <c r="C75" s="21"/>
-      <c r="D75" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>123</v>
+      <c r="D75" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="F75" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G75" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G75" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J75" s="6">
         <v>43844</v>
@@ -3160,22 +3165,22 @@
       <c r="B76" s="21"/>
       <c r="C76" s="21"/>
       <c r="D76" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>94</v>
       </c>
       <c r="F76" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G76" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G76" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J76" s="6">
         <v>43844</v>
@@ -3189,22 +3194,22 @@
       <c r="B77" s="21"/>
       <c r="C77" s="21"/>
       <c r="D77" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="F77" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G77" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G77" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J77" s="6">
         <v>43844</v>
@@ -3218,22 +3223,22 @@
       <c r="B78" s="21"/>
       <c r="C78" s="22"/>
       <c r="D78" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F78" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G78" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G78" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J78" s="6">
         <v>43844</v>
@@ -3246,25 +3251,25 @@
       </c>
       <c r="B79" s="22"/>
       <c r="C79" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D79" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>129</v>
-      </c>
       <c r="F79" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G79" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G79" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="J79" s="6">
         <v>43844</v>
@@ -3276,16 +3281,16 @@
         <v>54</v>
       </c>
       <c r="B80" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="D80" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>12</v>
@@ -3307,10 +3312,10 @@
       <c r="B81" s="21"/>
       <c r="C81" s="21"/>
       <c r="D81" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>12</v>
@@ -3332,7 +3337,7 @@
       <c r="B82" s="21"/>
       <c r="C82" s="21"/>
       <c r="D82" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>94</v>
@@ -3357,10 +3362,10 @@
       <c r="B83" s="21"/>
       <c r="C83" s="21"/>
       <c r="D83" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>12</v>
@@ -3382,7 +3387,7 @@
       <c r="B84" s="21"/>
       <c r="C84" s="22"/>
       <c r="D84" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>58</v>
@@ -3406,13 +3411,13 @@
       </c>
       <c r="B85" s="22"/>
       <c r="C85" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>12</v>
@@ -3432,19 +3437,19 @@
         <v>60</v>
       </c>
       <c r="B86" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="C86" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="D86" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D86" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>12</v>
+      <c r="F86" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="G86" s="6">
         <v>43828</v>
@@ -3452,8 +3457,12 @@
       <c r="H86" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I86" s="5"/>
-      <c r="J86" s="5"/>
+      <c r="I86" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J86" s="6">
+        <v>43844</v>
+      </c>
       <c r="K86" s="5"/>
     </row>
     <row r="87" spans="1:11" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3463,13 +3472,13 @@
       <c r="B87" s="21"/>
       <c r="C87" s="21"/>
       <c r="D87" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>12</v>
+        <v>143</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="G87" s="6">
         <v>43828</v>
@@ -3477,8 +3486,12 @@
       <c r="H87" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
+      <c r="I87" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J87" s="6">
+        <v>43844</v>
+      </c>
       <c r="K87" s="5"/>
     </row>
     <row r="88" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3488,13 +3501,13 @@
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
       <c r="D88" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F88" s="5" t="s">
-        <v>12</v>
+      <c r="F88" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="G88" s="6">
         <v>43828</v>
@@ -3502,8 +3515,12 @@
       <c r="H88" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I88" s="5"/>
-      <c r="J88" s="5"/>
+      <c r="I88" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J88" s="6">
+        <v>43844</v>
+      </c>
       <c r="K88" s="5"/>
     </row>
     <row r="89" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -3513,13 +3530,13 @@
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
       <c r="D89" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>12</v>
+      <c r="F89" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="G89" s="6">
         <v>43828</v>
@@ -3527,8 +3544,12 @@
       <c r="H89" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I89" s="5"/>
-      <c r="J89" s="5"/>
+      <c r="I89" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J89" s="6">
+        <v>43844</v>
+      </c>
       <c r="K89" s="5"/>
     </row>
     <row r="90" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3538,13 +3559,13 @@
       <c r="B90" s="21"/>
       <c r="C90" s="22"/>
       <c r="D90" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F90" s="5" t="s">
-        <v>12</v>
+      <c r="F90" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="G90" s="6">
         <v>43828</v>
@@ -3552,8 +3573,12 @@
       <c r="H90" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
+      <c r="I90" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J90" s="6">
+        <v>43844</v>
+      </c>
       <c r="K90" s="5"/>
     </row>
     <row r="91" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3562,16 +3587,16 @@
       </c>
       <c r="B91" s="22"/>
       <c r="C91" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>12</v>
+        <v>149</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="G91" s="6">
         <v>43828</v>
@@ -3579,13 +3604,17 @@
       <c r="H91" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
+      <c r="I91" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J91" s="6">
+        <v>43844</v>
+      </c>
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -3608,7 +3637,7 @@
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
@@ -3623,7 +3652,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>2</v>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9B1048-7289-4CD4-A8EA-2D7457C68501}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED2794C-5BE0-44C3-B3F9-4EA081EE8618}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-195" yWindow="1110" windowWidth="24330" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="171">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -724,7 +724,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -762,6 +762,21 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,18 +796,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1236,19 +1239,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1704,19 +1707,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1757,7 +1760,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1790,7 +1793,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="21"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1823,7 +1826,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="21"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1856,7 +1859,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="21"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1889,7 +1892,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="22"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1918,10 +1921,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="14" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1951,8 +1954,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -1980,8 +1983,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -2009,8 +2012,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -2034,8 +2037,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="22"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="16"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2059,7 +2062,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="21"/>
+      <c r="B37" s="15"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2090,10 +2093,10 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="17" t="s">
         <v>158</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -2123,8 +2126,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2152,8 +2155,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2183,8 +2186,8 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
@@ -2214,8 +2217,8 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
@@ -2243,8 +2246,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2272,10 +2275,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="14" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2301,8 +2304,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2326,8 +2329,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2351,8 +2354,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2376,8 +2379,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="21"/>
-      <c r="C48" s="22"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="16"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2401,7 +2404,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="22"/>
+      <c r="B49" s="16"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2428,10 +2431,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2457,8 +2460,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2482,8 +2485,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2507,8 +2510,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2532,8 +2535,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="21"/>
-      <c r="C54" s="22"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="16"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2557,7 +2560,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="22"/>
+      <c r="B55" s="16"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2584,10 +2587,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="14" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2617,8 +2620,8 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
       <c r="D57" s="11" t="s">
         <v>163</v>
       </c>
@@ -2646,8 +2649,8 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
       <c r="D58" s="7" t="s">
         <v>93</v>
       </c>
@@ -2675,8 +2678,8 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
       <c r="D59" s="5" t="s">
         <v>95</v>
       </c>
@@ -2704,8 +2707,8 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="21"/>
-      <c r="C60" s="22"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="16"/>
       <c r="D60" s="5" t="s">
         <v>97</v>
       </c>
@@ -2733,7 +2736,7 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="22"/>
+      <c r="B61" s="16"/>
       <c r="C61" s="5" t="s">
         <v>98</v>
       </c>
@@ -2764,10 +2767,10 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="14" t="s">
         <v>101</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2797,8 +2800,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15"/>
       <c r="D63" s="5" t="s">
         <v>103</v>
       </c>
@@ -2826,8 +2829,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15"/>
       <c r="D64" s="5" t="s">
         <v>104</v>
       </c>
@@ -2855,8 +2858,8 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
       <c r="D65" s="5" t="s">
         <v>105</v>
       </c>
@@ -2884,8 +2887,8 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="21"/>
-      <c r="C66" s="22"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="16"/>
       <c r="D66" s="5" t="s">
         <v>106</v>
       </c>
@@ -2913,7 +2916,7 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="22"/>
+      <c r="B67" s="16"/>
       <c r="C67" s="5" t="s">
         <v>107</v>
       </c>
@@ -2944,10 +2947,10 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="14" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -2956,8 +2959,8 @@
       <c r="E68" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F68" s="5" t="s">
-        <v>12</v>
+      <c r="F68" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G68" s="6">
         <v>43828</v>
@@ -2965,24 +2968,28 @@
       <c r="H68" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
+      <c r="I68" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J68" s="6">
+        <v>43845</v>
+      </c>
       <c r="K68" s="5"/>
     </row>
     <row r="69" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15"/>
       <c r="D69" s="5" t="s">
         <v>112</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F69" s="5" t="s">
-        <v>12</v>
+      <c r="F69" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G69" s="6">
         <v>43828</v>
@@ -2990,24 +2997,28 @@
       <c r="H69" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
+      <c r="I69" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J69" s="6">
+        <v>43845</v>
+      </c>
       <c r="K69" s="5"/>
     </row>
     <row r="70" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="21"/>
-      <c r="C70" s="21"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
       <c r="D70" s="5" t="s">
         <v>114</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F70" s="5" t="s">
-        <v>12</v>
+      <c r="F70" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G70" s="6">
         <v>43828</v>
@@ -3015,24 +3026,28 @@
       <c r="H70" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
+      <c r="I70" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J70" s="6">
+        <v>43845</v>
+      </c>
       <c r="K70" s="5"/>
     </row>
     <row r="71" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
       <c r="D71" s="5" t="s">
         <v>115</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F71" s="5" t="s">
-        <v>12</v>
+      <c r="F71" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G71" s="6">
         <v>43828</v>
@@ -3040,24 +3055,28 @@
       <c r="H71" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
+      <c r="I71" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J71" s="6">
+        <v>43845</v>
+      </c>
       <c r="K71" s="5"/>
     </row>
     <row r="72" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="21"/>
-      <c r="C72" s="22"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="16"/>
       <c r="D72" s="5" t="s">
         <v>117</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F72" s="5" t="s">
-        <v>12</v>
+      <c r="F72" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G72" s="6">
         <v>43828</v>
@@ -3065,15 +3084,19 @@
       <c r="H72" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
+      <c r="I72" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J72" s="6">
+        <v>43845</v>
+      </c>
       <c r="K72" s="5"/>
     </row>
     <row r="73" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="22"/>
+      <c r="B73" s="16"/>
       <c r="C73" s="5" t="s">
         <v>118</v>
       </c>
@@ -3083,8 +3106,8 @@
       <c r="E73" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F73" s="5" t="s">
-        <v>12</v>
+      <c r="F73" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G73" s="6">
         <v>43828</v>
@@ -3092,18 +3115,22 @@
       <c r="H73" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
+      <c r="I73" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J73" s="6">
+        <v>43845</v>
+      </c>
       <c r="K73" s="5"/>
     </row>
     <row r="74" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="20" t="s">
+      <c r="B74" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="20" t="s">
+      <c r="C74" s="14" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -3133,8 +3160,8 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
       <c r="D75" s="9" t="s">
         <v>170</v>
       </c>
@@ -3162,8 +3189,8 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15"/>
       <c r="D76" s="5" t="s">
         <v>123</v>
       </c>
@@ -3191,8 +3218,8 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="21"/>
-      <c r="C77" s="21"/>
+      <c r="B77" s="15"/>
+      <c r="C77" s="15"/>
       <c r="D77" s="5" t="s">
         <v>124</v>
       </c>
@@ -3220,8 +3247,8 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="21"/>
-      <c r="C78" s="22"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="16"/>
       <c r="D78" s="5" t="s">
         <v>126</v>
       </c>
@@ -3249,7 +3276,7 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="22"/>
+      <c r="B79" s="16"/>
       <c r="C79" s="5" t="s">
         <v>127</v>
       </c>
@@ -3280,10 +3307,10 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="14" t="s">
         <v>130</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -3292,8 +3319,8 @@
       <c r="E80" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F80" s="5" t="s">
-        <v>12</v>
+      <c r="F80" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G80" s="6">
         <v>43828</v>
@@ -3301,24 +3328,28 @@
       <c r="H80" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I80" s="5"/>
-      <c r="J80" s="5"/>
+      <c r="I80" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J80" s="6">
+        <v>43845</v>
+      </c>
       <c r="K80" s="5"/>
     </row>
     <row r="81" spans="1:11" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="21"/>
-      <c r="C81" s="21"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
       <c r="D81" s="5" t="s">
         <v>132</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F81" s="5" t="s">
-        <v>12</v>
+      <c r="F81" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G81" s="6">
         <v>43828</v>
@@ -3326,24 +3357,28 @@
       <c r="H81" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
+      <c r="I81" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J81" s="6">
+        <v>43845</v>
+      </c>
       <c r="K81" s="5"/>
     </row>
     <row r="82" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="21"/>
-      <c r="C82" s="21"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="15"/>
       <c r="D82" s="5" t="s">
         <v>134</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F82" s="5" t="s">
-        <v>12</v>
+      <c r="F82" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G82" s="6">
         <v>43828</v>
@@ -3351,24 +3386,28 @@
       <c r="H82" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I82" s="5"/>
-      <c r="J82" s="5"/>
+      <c r="I82" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J82" s="6">
+        <v>43845</v>
+      </c>
       <c r="K82" s="5"/>
     </row>
     <row r="83" spans="1:11" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="21"/>
-      <c r="C83" s="21"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
       <c r="D83" s="5" t="s">
         <v>135</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F83" s="5" t="s">
-        <v>12</v>
+      <c r="F83" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G83" s="6">
         <v>43828</v>
@@ -3376,24 +3415,28 @@
       <c r="H83" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I83" s="5"/>
-      <c r="J83" s="5"/>
+      <c r="I83" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J83" s="6">
+        <v>43845</v>
+      </c>
       <c r="K83" s="5"/>
     </row>
     <row r="84" spans="1:11" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="21"/>
-      <c r="C84" s="22"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="16"/>
       <c r="D84" s="5" t="s">
         <v>137</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F84" s="5" t="s">
-        <v>12</v>
+      <c r="F84" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G84" s="6">
         <v>43828</v>
@@ -3401,15 +3444,19 @@
       <c r="H84" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I84" s="5"/>
-      <c r="J84" s="5"/>
+      <c r="I84" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J84" s="6">
+        <v>43845</v>
+      </c>
       <c r="K84" s="5"/>
     </row>
     <row r="85" spans="1:11" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="22"/>
+      <c r="B85" s="16"/>
       <c r="C85" s="5" t="s">
         <v>138</v>
       </c>
@@ -3419,8 +3466,8 @@
       <c r="E85" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F85" s="5" t="s">
-        <v>12</v>
+      <c r="F85" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="G85" s="6">
         <v>43828</v>
@@ -3428,18 +3475,22 @@
       <c r="H85" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I85" s="5"/>
-      <c r="J85" s="5"/>
+      <c r="I85" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J85" s="6">
+        <v>43845</v>
+      </c>
       <c r="K85" s="5"/>
     </row>
     <row r="86" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="20" t="s">
+      <c r="B86" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="14" t="s">
         <v>141</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -3469,8 +3520,8 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="21"/>
-      <c r="C87" s="21"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="15"/>
       <c r="D87" s="5" t="s">
         <v>143</v>
       </c>
@@ -3498,8 +3549,8 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="21"/>
-      <c r="C88" s="21"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="15"/>
       <c r="D88" s="5" t="s">
         <v>144</v>
       </c>
@@ -3527,8 +3578,8 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="21"/>
-      <c r="C89" s="21"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
       <c r="D89" s="5" t="s">
         <v>145</v>
       </c>
@@ -3556,8 +3607,8 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="21"/>
-      <c r="C90" s="22"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="16"/>
       <c r="D90" s="5" t="s">
         <v>147</v>
       </c>
@@ -3585,7 +3636,7 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="22"/>
+      <c r="B91" s="16"/>
       <c r="C91" s="5" t="s">
         <v>148</v>
       </c>
@@ -3613,15 +3664,15 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="18"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3636,19 +3687,19 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="17" t="s">
+      <c r="A97" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="19"/>
-      <c r="K97" s="19"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="24"/>
+      <c r="K97" s="24"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
@@ -3687,15 +3738,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A92:G92"/>
@@ -3712,6 +3754,15 @@
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED2794C-5BE0-44C3-B3F9-4EA081EE8618}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3433F07-922B-439F-8609-7348EB886DEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2505" yWindow="825" windowWidth="24330" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="178">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -415,22 +415,13 @@
     <t>用户列表</t>
   </si>
   <si>
-    <t>表格形式显示用户列表，表格上面有查询表单，通过username、tel、email模糊查询</t>
-  </si>
-  <si>
     <t>根据username、tel、email模糊查询用户</t>
   </si>
   <si>
-    <t>根据username、tel、email字段模糊查询用户列表</t>
-  </si>
-  <si>
     <t>删除用户</t>
   </si>
   <si>
     <t>编辑用户</t>
-  </si>
-  <si>
-    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性有username、qq、tel、email</t>
   </si>
   <si>
     <t>恢复用户</t>
@@ -552,6 +543,46 @@
   </si>
   <si>
     <t>根据name、owner字段模糊查询</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间轴管理</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间轴列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间轴列表表格</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>未解决</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间轴应该根据pushDate降序排序</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格形式显示用户列表，表格上面有查询表单，通过username、tel、email模糊查询</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮跳转到新的tab栏，新的tab栏显示所有属性，能够编辑的属性有username、qq、tel、email</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格操作栏按钮，点击按钮弹出提示，点击确认发送ajax请求删除列表，并且删除相关缓存</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据username、tel、email字段模糊查询用户列表</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -763,6 +794,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1221,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" style="3" customWidth="1"/>
@@ -1239,19 +1276,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1707,19 +1744,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1760,7 +1797,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1793,7 +1830,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="15"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1826,7 +1863,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="15"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1859,7 +1896,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="15"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1892,7 +1929,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="16"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1921,10 +1958,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1954,8 +1991,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -1983,8 +2020,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -2012,8 +2049,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -2021,7 +2058,7 @@
         <v>41</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G35" s="6">
         <v>43828</v>
@@ -2037,8 +2074,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="16"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="18"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2046,7 +2083,7 @@
         <v>43</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G36" s="6">
         <v>43828</v>
@@ -2062,7 +2099,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="15"/>
+      <c r="B37" s="17"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2073,16 +2110,16 @@
         <v>46</v>
       </c>
       <c r="F37" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G37" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="9" t="s">
         <v>154</v>
-      </c>
-      <c r="G37" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="J37" s="6">
         <v>43840</v>
@@ -2093,11 +2130,11 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>158</v>
+      <c r="C38" s="19" t="s">
+        <v>155</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>48</v>
@@ -2106,16 +2143,16 @@
         <v>49</v>
       </c>
       <c r="F38" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G38" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="9" t="s">
         <v>154</v>
-      </c>
-      <c r="G38" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="J38" s="6">
         <v>43840</v>
@@ -2126,8 +2163,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2135,7 +2172,7 @@
         <v>51</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G39" s="6">
         <v>43828</v>
@@ -2144,7 +2181,7 @@
         <v>13</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J39" s="6">
         <v>43839</v>
@@ -2155,8 +2192,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2164,7 +2201,7 @@
         <v>53</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G40" s="6">
         <v>43828</v>
@@ -2173,7 +2210,7 @@
         <v>13</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J40" s="6">
         <v>43839</v>
@@ -2186,17 +2223,17 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>159</v>
-      </c>
       <c r="G41" s="6">
         <v>43828</v>
       </c>
@@ -2204,7 +2241,7 @@
         <v>13</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J41" s="6">
         <v>43840</v>
@@ -2217,16 +2254,16 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G42" s="6">
         <v>43828</v>
@@ -2235,7 +2272,7 @@
         <v>13</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J42" s="6">
         <v>43839</v>
@@ -2246,8 +2283,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2255,7 +2292,7 @@
         <v>60</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G43" s="6">
         <v>43828</v>
@@ -2264,7 +2301,7 @@
         <v>13</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J43" s="6">
         <v>43841</v>
@@ -2275,10 +2312,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="16" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2304,8 +2341,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2329,8 +2366,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2354,8 +2391,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2379,8 +2416,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="16"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2404,7 +2441,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="16"/>
+      <c r="B49" s="18"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2431,10 +2468,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="16" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2460,8 +2497,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2485,8 +2522,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2510,8 +2547,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2535,8 +2572,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="16"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2560,7 +2597,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="16"/>
+      <c r="B55" s="18"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2587,10 +2624,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="16" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2600,7 +2637,7 @@
         <v>92</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G56" s="6">
         <v>43828</v>
@@ -2609,7 +2646,7 @@
         <v>13</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J56" s="6">
         <v>43841</v>
@@ -2620,16 +2657,16 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
       <c r="D57" s="11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G57" s="6">
         <v>43828</v>
@@ -2638,7 +2675,7 @@
         <v>13</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J57" s="12">
         <v>43841</v>
@@ -2649,8 +2686,8 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
       <c r="D58" s="7" t="s">
         <v>93</v>
       </c>
@@ -2658,7 +2695,7 @@
         <v>94</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G58" s="6">
         <v>43828</v>
@@ -2667,7 +2704,7 @@
         <v>13</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J58" s="12">
         <v>43841</v>
@@ -2678,8 +2715,8 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
       <c r="D59" s="5" t="s">
         <v>95</v>
       </c>
@@ -2687,7 +2724,7 @@
         <v>96</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G59" s="6">
         <v>43828</v>
@@ -2696,7 +2733,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J59" s="12">
         <v>43841</v>
@@ -2707,8 +2744,8 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="16"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
       <c r="D60" s="5" t="s">
         <v>97</v>
       </c>
@@ -2716,7 +2753,7 @@
         <v>58</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G60" s="6">
         <v>43828</v>
@@ -2725,7 +2762,7 @@
         <v>13</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J60" s="12">
         <v>43841</v>
@@ -2736,7 +2773,7 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="16"/>
+      <c r="B61" s="18"/>
       <c r="C61" s="5" t="s">
         <v>98</v>
       </c>
@@ -2747,7 +2784,7 @@
         <v>99</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G61" s="6">
         <v>43828</v>
@@ -2756,7 +2793,7 @@
         <v>13</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J61" s="12">
         <v>43841</v>
@@ -2767,10 +2804,10 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="16" t="s">
         <v>101</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2780,7 +2817,7 @@
         <v>102</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G62" s="6">
         <v>43828</v>
@@ -2789,7 +2826,7 @@
         <v>13</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J62" s="12">
         <v>43843</v>
@@ -2800,8 +2837,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
       <c r="D63" s="5" t="s">
         <v>103</v>
       </c>
@@ -2809,7 +2846,7 @@
         <v>103</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G63" s="6">
         <v>43828</v>
@@ -2818,7 +2855,7 @@
         <v>13</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J63" s="12">
         <v>43843</v>
@@ -2829,8 +2866,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
       <c r="D64" s="5" t="s">
         <v>104</v>
       </c>
@@ -2838,7 +2875,7 @@
         <v>94</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G64" s="6">
         <v>43828</v>
@@ -2847,7 +2884,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J64" s="12">
         <v>43843</v>
@@ -2858,16 +2895,16 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
       <c r="D65" s="5" t="s">
         <v>105</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G65" s="6">
         <v>43828</v>
@@ -2876,7 +2913,7 @@
         <v>13</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J65" s="12">
         <v>43843</v>
@@ -2887,8 +2924,8 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="16"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="18"/>
       <c r="D66" s="5" t="s">
         <v>106</v>
       </c>
@@ -2896,7 +2933,7 @@
         <v>58</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G66" s="6">
         <v>43828</v>
@@ -2905,7 +2942,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J66" s="12">
         <v>43843</v>
@@ -2916,7 +2953,7 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="16"/>
+      <c r="B67" s="18"/>
       <c r="C67" s="5" t="s">
         <v>107</v>
       </c>
@@ -2927,7 +2964,7 @@
         <v>108</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G67" s="6">
         <v>43828</v>
@@ -2936,7 +2973,7 @@
         <v>13</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J67" s="12">
         <v>43843</v>
@@ -2947,10 +2984,10 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="16" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -2960,7 +2997,7 @@
         <v>111</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G68" s="6">
         <v>43828</v>
@@ -2969,7 +3006,7 @@
         <v>13</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J68" s="6">
         <v>43845</v>
@@ -2980,8 +3017,8 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
       <c r="D69" s="5" t="s">
         <v>112</v>
       </c>
@@ -2989,7 +3026,7 @@
         <v>113</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G69" s="6">
         <v>43828</v>
@@ -2998,7 +3035,7 @@
         <v>13</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J69" s="6">
         <v>43845</v>
@@ -3009,8 +3046,8 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
       <c r="D70" s="5" t="s">
         <v>114</v>
       </c>
@@ -3018,7 +3055,7 @@
         <v>94</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G70" s="6">
         <v>43828</v>
@@ -3027,7 +3064,7 @@
         <v>13</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J70" s="6">
         <v>43845</v>
@@ -3038,8 +3075,8 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
       <c r="D71" s="5" t="s">
         <v>115</v>
       </c>
@@ -3047,7 +3084,7 @@
         <v>116</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G71" s="6">
         <v>43828</v>
@@ -3056,7 +3093,7 @@
         <v>13</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J71" s="6">
         <v>43845</v>
@@ -3067,8 +3104,8 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="16"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="18"/>
       <c r="D72" s="5" t="s">
         <v>117</v>
       </c>
@@ -3076,7 +3113,7 @@
         <v>58</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G72" s="6">
         <v>43828</v>
@@ -3085,7 +3122,7 @@
         <v>13</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J72" s="6">
         <v>43845</v>
@@ -3096,7 +3133,7 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="16"/>
+      <c r="B73" s="18"/>
       <c r="C73" s="5" t="s">
         <v>118</v>
       </c>
@@ -3107,7 +3144,7 @@
         <v>119</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G73" s="6">
         <v>43828</v>
@@ -3116,7 +3153,7 @@
         <v>13</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J73" s="6">
         <v>43845</v>
@@ -3127,10 +3164,10 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="16" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -3140,7 +3177,7 @@
         <v>122</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G74" s="6">
         <v>43828</v>
@@ -3149,7 +3186,7 @@
         <v>13</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J74" s="6">
         <v>43844</v>
@@ -3160,16 +3197,16 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
       <c r="D75" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G75" s="6">
         <v>43828</v>
@@ -3178,7 +3215,7 @@
         <v>13</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J75" s="6">
         <v>43844</v>
@@ -3189,8 +3226,8 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
       <c r="D76" s="5" t="s">
         <v>123</v>
       </c>
@@ -3198,7 +3235,7 @@
         <v>94</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G76" s="6">
         <v>43828</v>
@@ -3207,7 +3244,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J76" s="6">
         <v>43844</v>
@@ -3218,8 +3255,8 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
       <c r="D77" s="5" t="s">
         <v>124</v>
       </c>
@@ -3227,7 +3264,7 @@
         <v>125</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G77" s="6">
         <v>43828</v>
@@ -3236,7 +3273,7 @@
         <v>13</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J77" s="6">
         <v>43844</v>
@@ -3247,8 +3284,8 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="15"/>
-      <c r="C78" s="16"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="18"/>
       <c r="D78" s="5" t="s">
         <v>126</v>
       </c>
@@ -3256,7 +3293,7 @@
         <v>58</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G78" s="6">
         <v>43828</v>
@@ -3265,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J78" s="6">
         <v>43844</v>
@@ -3276,7 +3313,7 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="16"/>
+      <c r="B79" s="18"/>
       <c r="C79" s="5" t="s">
         <v>127</v>
       </c>
@@ -3287,7 +3324,7 @@
         <v>128</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G79" s="6">
         <v>43828</v>
@@ -3296,7 +3333,7 @@
         <v>13</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J79" s="6">
         <v>43844</v>
@@ -3307,20 +3344,20 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>131</v>
+      <c r="E80" s="9" t="s">
+        <v>174</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G80" s="6">
         <v>43828</v>
@@ -3329,7 +3366,7 @@
         <v>13</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J80" s="6">
         <v>43845</v>
@@ -3340,16 +3377,16 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="15"/>
-      <c r="C81" s="15"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
       <c r="D81" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G81" s="6">
         <v>43828</v>
@@ -3358,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J81" s="6">
         <v>43845</v>
@@ -3369,16 +3406,16 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
       <c r="D82" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>94</v>
+        <v>132</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G82" s="6">
         <v>43828</v>
@@ -3387,7 +3424,7 @@
         <v>13</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J82" s="6">
         <v>43845</v>
@@ -3398,16 +3435,16 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="15"/>
-      <c r="C83" s="15"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
       <c r="D83" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G83" s="6">
         <v>43828</v>
@@ -3416,7 +3453,7 @@
         <v>13</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J83" s="6">
         <v>43845</v>
@@ -3427,16 +3464,16 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="16"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="18"/>
       <c r="D84" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G84" s="6">
         <v>43828</v>
@@ -3445,7 +3482,7 @@
         <v>13</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J84" s="6">
         <v>43845</v>
@@ -3456,18 +3493,18 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="16"/>
+      <c r="B85" s="18"/>
       <c r="C85" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G85" s="6">
         <v>43828</v>
@@ -3476,7 +3513,7 @@
         <v>13</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J85" s="6">
         <v>43845</v>
@@ -3487,20 +3524,20 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>141</v>
+      <c r="B86" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>138</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G86" s="6">
         <v>43828</v>
@@ -3509,7 +3546,7 @@
         <v>13</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J86" s="6">
         <v>43844</v>
@@ -3520,16 +3557,16 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="15"/>
-      <c r="C87" s="15"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
       <c r="D87" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G87" s="6">
         <v>43828</v>
@@ -3538,7 +3575,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J87" s="6">
         <v>43844</v>
@@ -3549,16 +3586,16 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
       <c r="D88" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>94</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G88" s="6">
         <v>43828</v>
@@ -3567,7 +3604,7 @@
         <v>13</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J88" s="6">
         <v>43844</v>
@@ -3578,16 +3615,16 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
       <c r="D89" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G89" s="6">
         <v>43828</v>
@@ -3596,7 +3633,7 @@
         <v>13</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J89" s="6">
         <v>43844</v>
@@ -3607,16 +3644,16 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="15"/>
-      <c r="C90" s="16"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="18"/>
       <c r="D90" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G90" s="6">
         <v>43828</v>
@@ -3625,7 +3662,7 @@
         <v>13</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J90" s="6">
         <v>43844</v>
@@ -3636,18 +3673,18 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="16"/>
+      <c r="B91" s="18"/>
       <c r="C91" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>118</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G91" s="6">
         <v>43828</v>
@@ -3656,7 +3693,7 @@
         <v>13</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J91" s="6">
         <v>43844</v>
@@ -3664,15 +3701,15 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
+      <c r="A92" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3687,23 +3724,23 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B97" s="24"/>
-      <c r="C97" s="24"/>
-      <c r="D97" s="24"/>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="24"/>
-      <c r="J97" s="24"/>
-      <c r="K97" s="24"/>
+      <c r="A97" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="26"/>
+      <c r="J97" s="26"/>
+      <c r="K97" s="26"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>2</v>
@@ -3736,6 +3773,35 @@
         <v>11</v>
       </c>
     </row>
+    <row r="99" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="3">
+        <v>1</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D99" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F99" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="G99" s="15">
+        <v>43848</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="A1:K1"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3433F07-922B-439F-8609-7348EB886DEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0DBC0D-34C9-484F-964B-5E2E505B23AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="825" windowWidth="24330" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="177">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -461,11 +461,6 @@
   </si>
   <si>
     <t>点击进入新的tab页面，需要填写的字段有content</t>
-  </si>
-  <si>
-    <t>备注： controller层异常  
-搜索框没做
-result.html  article部分需要修改</t>
   </si>
   <si>
     <t>BUG清单</t>
@@ -755,7 +750,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -802,16 +797,7 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -829,11 +815,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1276,19 +1277,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1744,19 +1745,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1797,7 +1798,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1830,7 +1831,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="17"/>
+      <c r="B28" s="24"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1863,7 +1864,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="17"/>
+      <c r="B29" s="24"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1896,7 +1897,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="17"/>
+      <c r="B30" s="24"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1929,7 +1930,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="18"/>
+      <c r="B31" s="25"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1958,10 +1959,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="23" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1991,8 +1992,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -2020,8 +2021,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -2049,8 +2050,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -2058,7 +2059,7 @@
         <v>41</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G35" s="6">
         <v>43828</v>
@@ -2074,8 +2075,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="18"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>43</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G36" s="6">
         <v>43828</v>
@@ -2099,7 +2100,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="17"/>
+      <c r="B37" s="24"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2110,7 +2111,7 @@
         <v>46</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G37" s="6">
         <v>43828</v>
@@ -2119,7 +2120,7 @@
         <v>13</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J37" s="6">
         <v>43840</v>
@@ -2130,11 +2131,11 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="19" t="s">
-        <v>155</v>
+      <c r="C38" s="26" t="s">
+        <v>154</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>48</v>
@@ -2143,7 +2144,7 @@
         <v>49</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G38" s="6">
         <v>43828</v>
@@ -2152,7 +2153,7 @@
         <v>13</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J38" s="6">
         <v>43840</v>
@@ -2163,8 +2164,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2172,16 +2173,16 @@
         <v>51</v>
       </c>
       <c r="F39" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G39" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J39" s="6">
         <v>43839</v>
@@ -2192,8 +2193,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2201,16 +2202,16 @@
         <v>53</v>
       </c>
       <c r="F40" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G40" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J40" s="6">
         <v>43839</v>
@@ -2223,25 +2224,25 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G41" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="G41" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="J41" s="6">
         <v>43840</v>
@@ -2254,25 +2255,25 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G42" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G42" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J42" s="6">
         <v>43839</v>
@@ -2283,8 +2284,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2292,7 +2293,7 @@
         <v>60</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G43" s="6">
         <v>43828</v>
@@ -2301,7 +2302,7 @@
         <v>13</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J43" s="6">
         <v>43841</v>
@@ -2312,10 +2313,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="23" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2341,8 +2342,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2366,8 +2367,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2391,8 +2392,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2416,8 +2417,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="25"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2441,7 +2442,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="18"/>
+      <c r="B49" s="25"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2468,10 +2469,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="23" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2497,8 +2498,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2522,8 +2523,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2547,8 +2548,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2572,8 +2573,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="25"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2597,7 +2598,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="18"/>
+      <c r="B55" s="25"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2624,10 +2625,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="23" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2637,7 +2638,7 @@
         <v>92</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G56" s="6">
         <v>43828</v>
@@ -2646,7 +2647,7 @@
         <v>13</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J56" s="6">
         <v>43841</v>
@@ -2657,16 +2658,16 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
       <c r="D57" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E57" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E57" s="11" t="s">
-        <v>161</v>
-      </c>
       <c r="F57" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G57" s="6">
         <v>43828</v>
@@ -2675,7 +2676,7 @@
         <v>13</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J57" s="12">
         <v>43841</v>
@@ -2686,8 +2687,8 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="7" t="s">
         <v>93</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>94</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G58" s="6">
         <v>43828</v>
@@ -2704,7 +2705,7 @@
         <v>13</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J58" s="12">
         <v>43841</v>
@@ -2715,8 +2716,8 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="5" t="s">
         <v>95</v>
       </c>
@@ -2724,7 +2725,7 @@
         <v>96</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G59" s="6">
         <v>43828</v>
@@ -2733,7 +2734,7 @@
         <v>13</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J59" s="12">
         <v>43841</v>
@@ -2744,8 +2745,8 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="25"/>
       <c r="D60" s="5" t="s">
         <v>97</v>
       </c>
@@ -2753,7 +2754,7 @@
         <v>58</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G60" s="6">
         <v>43828</v>
@@ -2762,7 +2763,7 @@
         <v>13</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J60" s="12">
         <v>43841</v>
@@ -2773,7 +2774,7 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="18"/>
+      <c r="B61" s="25"/>
       <c r="C61" s="5" t="s">
         <v>98</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>99</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G61" s="6">
         <v>43828</v>
@@ -2793,7 +2794,7 @@
         <v>13</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J61" s="12">
         <v>43841</v>
@@ -2804,10 +2805,10 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="23" t="s">
         <v>101</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2817,7 +2818,7 @@
         <v>102</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G62" s="6">
         <v>43828</v>
@@ -2826,7 +2827,7 @@
         <v>13</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J62" s="12">
         <v>43843</v>
@@ -2837,8 +2838,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
       <c r="D63" s="5" t="s">
         <v>103</v>
       </c>
@@ -2846,7 +2847,7 @@
         <v>103</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G63" s="6">
         <v>43828</v>
@@ -2855,7 +2856,7 @@
         <v>13</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J63" s="12">
         <v>43843</v>
@@ -2866,8 +2867,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="5" t="s">
         <v>104</v>
       </c>
@@ -2875,7 +2876,7 @@
         <v>94</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G64" s="6">
         <v>43828</v>
@@ -2884,7 +2885,7 @@
         <v>13</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J64" s="12">
         <v>43843</v>
@@ -2895,16 +2896,16 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="5" t="s">
         <v>105</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G65" s="6">
         <v>43828</v>
@@ -2913,7 +2914,7 @@
         <v>13</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J65" s="12">
         <v>43843</v>
@@ -2924,8 +2925,8 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="25"/>
       <c r="D66" s="5" t="s">
         <v>106</v>
       </c>
@@ -2933,7 +2934,7 @@
         <v>58</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G66" s="6">
         <v>43828</v>
@@ -2942,7 +2943,7 @@
         <v>13</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J66" s="12">
         <v>43843</v>
@@ -2953,7 +2954,7 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="18"/>
+      <c r="B67" s="25"/>
       <c r="C67" s="5" t="s">
         <v>107</v>
       </c>
@@ -2964,7 +2965,7 @@
         <v>108</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G67" s="6">
         <v>43828</v>
@@ -2973,7 +2974,7 @@
         <v>13</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J67" s="12">
         <v>43843</v>
@@ -2984,10 +2985,10 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -2997,16 +2998,16 @@
         <v>111</v>
       </c>
       <c r="F68" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G68" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="G68" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I68" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="J68" s="6">
         <v>43845</v>
@@ -3017,8 +3018,8 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
       <c r="D69" s="5" t="s">
         <v>112</v>
       </c>
@@ -3026,16 +3027,16 @@
         <v>113</v>
       </c>
       <c r="F69" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G69" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="G69" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I69" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="J69" s="6">
         <v>43845</v>
@@ -3046,8 +3047,8 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
       <c r="D70" s="5" t="s">
         <v>114</v>
       </c>
@@ -3055,16 +3056,16 @@
         <v>94</v>
       </c>
       <c r="F70" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G70" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="G70" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="J70" s="6">
         <v>43845</v>
@@ -3075,8 +3076,8 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="5" t="s">
         <v>115</v>
       </c>
@@ -3084,16 +3085,16 @@
         <v>116</v>
       </c>
       <c r="F71" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G71" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="G71" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="J71" s="6">
         <v>43845</v>
@@ -3104,8 +3105,8 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="18"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="5" t="s">
         <v>117</v>
       </c>
@@ -3113,16 +3114,16 @@
         <v>58</v>
       </c>
       <c r="F72" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G72" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="G72" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I72" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="J72" s="6">
         <v>43845</v>
@@ -3133,7 +3134,7 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="18"/>
+      <c r="B73" s="25"/>
       <c r="C73" s="5" t="s">
         <v>118</v>
       </c>
@@ -3144,16 +3145,16 @@
         <v>119</v>
       </c>
       <c r="F73" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G73" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="G73" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="J73" s="6">
         <v>43845</v>
@@ -3164,10 +3165,10 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="23" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -3177,16 +3178,16 @@
         <v>122</v>
       </c>
       <c r="F74" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G74" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="G74" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H74" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="J74" s="6">
         <v>43844</v>
@@ -3197,25 +3198,25 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F75" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G75" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="G75" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="J75" s="6">
         <v>43844</v>
@@ -3226,8 +3227,8 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
       <c r="D76" s="5" t="s">
         <v>123</v>
       </c>
@@ -3235,16 +3236,16 @@
         <v>94</v>
       </c>
       <c r="F76" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G76" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="G76" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="J76" s="6">
         <v>43844</v>
@@ -3255,8 +3256,8 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="5" t="s">
         <v>124</v>
       </c>
@@ -3264,16 +3265,16 @@
         <v>125</v>
       </c>
       <c r="F77" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G77" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="G77" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="J77" s="6">
         <v>43844</v>
@@ -3284,8 +3285,8 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="18"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="5" t="s">
         <v>126</v>
       </c>
@@ -3293,16 +3294,16 @@
         <v>58</v>
       </c>
       <c r="F78" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G78" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="G78" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H78" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="J78" s="6">
         <v>43844</v>
@@ -3313,7 +3314,7 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="18"/>
+      <c r="B79" s="25"/>
       <c r="C79" s="5" t="s">
         <v>127</v>
       </c>
@@ -3324,16 +3325,16 @@
         <v>128</v>
       </c>
       <c r="F79" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G79" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="G79" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="J79" s="6">
         <v>43844</v>
@@ -3344,29 +3345,29 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="23" t="s">
         <v>130</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>130</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F80" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G80" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G80" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J80" s="6">
         <v>43845</v>
@@ -3377,25 +3378,25 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
       <c r="D81" s="5" t="s">
         <v>131</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F81" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G81" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G81" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J81" s="6">
         <v>43845</v>
@@ -3406,25 +3407,25 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
+      <c r="B82" s="24"/>
+      <c r="C82" s="24"/>
       <c r="D82" s="5" t="s">
         <v>132</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F82" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G82" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G82" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J82" s="6">
         <v>43845</v>
@@ -3435,25 +3436,25 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="24"/>
       <c r="D83" s="5" t="s">
         <v>133</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F83" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G83" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G83" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J83" s="6">
         <v>43845</v>
@@ -3464,8 +3465,8 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="25"/>
       <c r="D84" s="5" t="s">
         <v>134</v>
       </c>
@@ -3473,16 +3474,16 @@
         <v>58</v>
       </c>
       <c r="F84" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G84" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G84" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I84" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J84" s="6">
         <v>43845</v>
@@ -3493,7 +3494,7 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="18"/>
+      <c r="B85" s="25"/>
       <c r="C85" s="5" t="s">
         <v>135</v>
       </c>
@@ -3504,16 +3505,16 @@
         <v>136</v>
       </c>
       <c r="F85" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G85" s="6">
+        <v>43828</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="G85" s="6">
-        <v>43828</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J85" s="6">
         <v>43845</v>
@@ -3524,10 +3525,10 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="C86" s="23" t="s">
         <v>138</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -3537,7 +3538,7 @@
         <v>139</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G86" s="6">
         <v>43828</v>
@@ -3546,7 +3547,7 @@
         <v>13</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J86" s="6">
         <v>43844</v>
@@ -3557,8 +3558,8 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
       <c r="D87" s="5" t="s">
         <v>140</v>
       </c>
@@ -3566,7 +3567,7 @@
         <v>140</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G87" s="6">
         <v>43828</v>
@@ -3575,7 +3576,7 @@
         <v>13</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J87" s="6">
         <v>43844</v>
@@ -3586,8 +3587,8 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="24"/>
       <c r="D88" s="5" t="s">
         <v>141</v>
       </c>
@@ -3595,7 +3596,7 @@
         <v>94</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G88" s="6">
         <v>43828</v>
@@ -3604,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J88" s="6">
         <v>43844</v>
@@ -3615,8 +3616,8 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="24"/>
       <c r="D89" s="5" t="s">
         <v>142</v>
       </c>
@@ -3624,7 +3625,7 @@
         <v>143</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G89" s="6">
         <v>43828</v>
@@ -3633,7 +3634,7 @@
         <v>13</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J89" s="6">
         <v>43844</v>
@@ -3644,8 +3645,8 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="18"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="25"/>
       <c r="D90" s="5" t="s">
         <v>144</v>
       </c>
@@ -3653,7 +3654,7 @@
         <v>58</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G90" s="6">
         <v>43828</v>
@@ -3662,7 +3663,7 @@
         <v>13</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J90" s="6">
         <v>43844</v>
@@ -3673,7 +3674,7 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="18"/>
+      <c r="B91" s="25"/>
       <c r="C91" s="5" t="s">
         <v>145</v>
       </c>
@@ -3684,7 +3685,7 @@
         <v>146</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G91" s="6">
         <v>43828</v>
@@ -3693,7 +3694,7 @@
         <v>13</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J91" s="6">
         <v>43844</v>
@@ -3701,15 +3702,17 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="B92" s="25"/>
-      <c r="C92" s="25"/>
-      <c r="D92" s="25"/>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25"/>
-      <c r="G92" s="25"/>
+      <c r="A92" s="27"/>
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+      <c r="K92" s="16"/>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G93" s="8"/>
@@ -3724,23 +3727,23 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
-      <c r="D97" s="26"/>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="26"/>
-      <c r="H97" s="26"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="26"/>
-      <c r="K97" s="26"/>
+      <c r="A97" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B97" s="22"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="22"/>
+      <c r="K97" s="22"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>2</v>
@@ -3778,35 +3781,43 @@
         <v>1</v>
       </c>
       <c r="B99" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C99" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="D99" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D99" s="14" t="s">
+      <c r="E99" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F99" s="14" t="s">
         <v>170</v>
-      </c>
-      <c r="E99" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F99" s="14" t="s">
-        <v>171</v>
       </c>
       <c r="G99" s="15">
         <v>43848</v>
       </c>
       <c r="H99" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="101" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="102" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="24">
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A92:G92"/>
     <mergeCell ref="A97:K97"/>
     <mergeCell ref="B27:B31"/>
     <mergeCell ref="B32:B37"/>
@@ -3820,15 +3831,6 @@
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0DBC0D-34C9-484F-964B-5E2E505B23AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30118FFB-28C0-4DEC-AB07-EB9E7012806C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4515" yWindow="885" windowWidth="24330" windowHeight="14625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="194">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -578,6 +578,74 @@
   </si>
   <si>
     <t>根据username、tel、email字段模糊查询用户列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>博客管理</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>博客新增</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增博客</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在发表博客的时候，如果summary为空，那么不会自动生成，应改成根据博客内容自动生成，而且在新增博客时没有抓取博客的第一张图片作为封面，应该修改</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>未解决</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>首页</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>导航栏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>导航菜单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>导航菜单在最小分辨率应该设计为崔才庆博客那种样式，要求点击导航按钮显示一个下拉菜单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜索</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示搜索栏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击搜索按钮应该在页面上显示一个搜索栏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文检索功能</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在搜索栏输入检索的文字之后，根据检索的文字跳转到博客文章的相关页面下</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>文章列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>文章列表的第一页是在项目启动的时候就加载了，改成请求时再加载</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -800,6 +868,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -817,24 +903,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,19 +1345,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1330,14 +1398,24 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="B3" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>186</v>
+      </c>
       <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="6">
+        <v>43861</v>
+      </c>
       <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
@@ -1349,14 +1427,24 @@
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="B4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>189</v>
+      </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6">
+        <v>43861</v>
+      </c>
       <c r="H4" s="5" t="s">
         <v>13</v>
       </c>
@@ -1368,14 +1456,24 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="B5" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>191</v>
+      </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="6">
+        <v>43861</v>
+      </c>
       <c r="H5" s="5" t="s">
         <v>13</v>
       </c>
@@ -1387,14 +1485,24 @@
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="B6" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>193</v>
+      </c>
       <c r="F6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6">
+        <v>43861</v>
+      </c>
       <c r="H6" s="5" t="s">
         <v>13</v>
       </c>
@@ -1745,19 +1853,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1798,7 +1906,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="19" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1831,7 +1939,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="24"/>
+      <c r="B28" s="20"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1864,7 +1972,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="24"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1897,7 +2005,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="24"/>
+      <c r="B30" s="20"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -1930,7 +2038,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="25"/>
+      <c r="B31" s="21"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -1959,10 +2067,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="19" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -1992,8 +2100,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -2021,8 +2129,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -2050,8 +2158,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -2075,8 +2183,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2100,7 +2208,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2131,10 +2239,10 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="22" t="s">
         <v>154</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -2164,8 +2272,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2193,8 +2301,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2224,8 +2332,8 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
@@ -2255,8 +2363,8 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
@@ -2284,8 +2392,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2313,10 +2421,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="19" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2342,8 +2450,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2367,8 +2475,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2392,8 +2500,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2417,8 +2525,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="24"/>
-      <c r="C48" s="25"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2442,7 +2550,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="25"/>
+      <c r="B49" s="21"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2469,10 +2577,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="19" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2498,8 +2606,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2523,8 +2631,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2548,8 +2656,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2573,8 +2681,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="24"/>
-      <c r="C54" s="25"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="21"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2598,7 +2706,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="25"/>
+      <c r="B55" s="21"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2625,10 +2733,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="19" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2658,8 +2766,8 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
       <c r="D57" s="11" t="s">
         <v>159</v>
       </c>
@@ -2687,8 +2795,8 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
       <c r="D58" s="7" t="s">
         <v>93</v>
       </c>
@@ -2716,8 +2824,8 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
       <c r="D59" s="5" t="s">
         <v>95</v>
       </c>
@@ -2745,8 +2853,8 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="24"/>
-      <c r="C60" s="25"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="21"/>
       <c r="D60" s="5" t="s">
         <v>97</v>
       </c>
@@ -2774,7 +2882,7 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="25"/>
+      <c r="B61" s="21"/>
       <c r="C61" s="5" t="s">
         <v>98</v>
       </c>
@@ -2805,10 +2913,10 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="19" t="s">
         <v>101</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2838,8 +2946,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
       <c r="D63" s="5" t="s">
         <v>103</v>
       </c>
@@ -2867,8 +2975,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
       <c r="D64" s="5" t="s">
         <v>104</v>
       </c>
@@ -2896,8 +3004,8 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
       <c r="D65" s="5" t="s">
         <v>105</v>
       </c>
@@ -2925,8 +3033,8 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="24"/>
-      <c r="C66" s="25"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="21"/>
       <c r="D66" s="5" t="s">
         <v>106</v>
       </c>
@@ -2954,7 +3062,7 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="25"/>
+      <c r="B67" s="21"/>
       <c r="C67" s="5" t="s">
         <v>107</v>
       </c>
@@ -2985,10 +3093,10 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="23" t="s">
+      <c r="B68" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="19" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -3018,8 +3126,8 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
       <c r="D69" s="5" t="s">
         <v>112</v>
       </c>
@@ -3047,8 +3155,8 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
       <c r="D70" s="5" t="s">
         <v>114</v>
       </c>
@@ -3076,8 +3184,8 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
       <c r="D71" s="5" t="s">
         <v>115</v>
       </c>
@@ -3105,8 +3213,8 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="24"/>
-      <c r="C72" s="25"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="21"/>
       <c r="D72" s="5" t="s">
         <v>117</v>
       </c>
@@ -3134,7 +3242,7 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="25"/>
+      <c r="B73" s="21"/>
       <c r="C73" s="5" t="s">
         <v>118</v>
       </c>
@@ -3165,10 +3273,10 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="23" t="s">
+      <c r="B74" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="19" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -3198,8 +3306,8 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
       <c r="D75" s="9" t="s">
         <v>166</v>
       </c>
@@ -3227,8 +3335,8 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="5" t="s">
         <v>123</v>
       </c>
@@ -3256,8 +3364,8 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
       <c r="D77" s="5" t="s">
         <v>124</v>
       </c>
@@ -3285,8 +3393,8 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="24"/>
-      <c r="C78" s="25"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="21"/>
       <c r="D78" s="5" t="s">
         <v>126</v>
       </c>
@@ -3314,7 +3422,7 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="25"/>
+      <c r="B79" s="21"/>
       <c r="C79" s="5" t="s">
         <v>127</v>
       </c>
@@ -3345,10 +3453,10 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="23" t="s">
+      <c r="B80" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="19" t="s">
         <v>130</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -3378,8 +3486,8 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="24"/>
-      <c r="C81" s="24"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
       <c r="D81" s="5" t="s">
         <v>131</v>
       </c>
@@ -3407,8 +3515,8 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="24"/>
-      <c r="C82" s="24"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
       <c r="D82" s="5" t="s">
         <v>132</v>
       </c>
@@ -3436,8 +3544,8 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
       <c r="D83" s="5" t="s">
         <v>133</v>
       </c>
@@ -3465,8 +3573,8 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="25"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="21"/>
       <c r="D84" s="5" t="s">
         <v>134</v>
       </c>
@@ -3494,7 +3602,7 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="25"/>
+      <c r="B85" s="21"/>
       <c r="C85" s="5" t="s">
         <v>135</v>
       </c>
@@ -3525,10 +3633,10 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="23" t="s">
+      <c r="B86" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="19" t="s">
         <v>138</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -3558,8 +3666,8 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="24"/>
-      <c r="C87" s="24"/>
+      <c r="B87" s="20"/>
+      <c r="C87" s="20"/>
       <c r="D87" s="5" t="s">
         <v>140</v>
       </c>
@@ -3587,8 +3695,8 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="24"/>
-      <c r="C88" s="24"/>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20"/>
       <c r="D88" s="5" t="s">
         <v>141</v>
       </c>
@@ -3616,8 +3724,8 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="24"/>
-      <c r="C89" s="24"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="20"/>
       <c r="D89" s="5" t="s">
         <v>142</v>
       </c>
@@ -3645,8 +3753,8 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="24"/>
-      <c r="C90" s="25"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="21"/>
       <c r="D90" s="5" t="s">
         <v>144</v>
       </c>
@@ -3674,7 +3782,7 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="25"/>
+      <c r="B91" s="21"/>
       <c r="C91" s="5" t="s">
         <v>145</v>
       </c>
@@ -3702,13 +3810,13 @@
       <c r="K91" s="5"/>
     </row>
     <row r="92" spans="1:11" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="27"/>
-      <c r="B92" s="28"/>
-      <c r="C92" s="28"/>
-      <c r="D92" s="28"/>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
       <c r="H92" s="16"/>
       <c r="I92" s="16"/>
       <c r="J92" s="16"/>
@@ -3727,21 +3835,21 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="21" t="s">
+      <c r="A97" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="B97" s="22"/>
-      <c r="C97" s="22"/>
-      <c r="D97" s="22"/>
-      <c r="E97" s="22"/>
-      <c r="F97" s="22"/>
-      <c r="G97" s="22"/>
-      <c r="H97" s="22"/>
-      <c r="I97" s="22"/>
-      <c r="J97" s="22"/>
-      <c r="K97" s="22"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B97" s="28"/>
+      <c r="C97" s="28"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="28"/>
+      <c r="J97" s="28"/>
+      <c r="K97" s="28"/>
+    </row>
+    <row r="98" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>148</v>
       </c>
@@ -3802,20 +3910,36 @@
         <v>171</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="3">
+        <v>2</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E100" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="G100" s="8">
+        <v>43861</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>182</v>
+      </c>
+    </row>
     <row r="101" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="102" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A97:K97"/>
@@ -3831,6 +3955,15 @@
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RootElement功能清单.xlsx
+++ b/RootElement功能清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\root_element\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30118FFB-28C0-4DEC-AB07-EB9E7012806C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C3497D-8225-41FE-8339-D93F64902294}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4515" yWindow="885" windowWidth="24330" windowHeight="14625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2385" yWindow="1080" windowWidth="22665" windowHeight="13515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="214">
   <si>
     <t>RootElement需求清单</t>
   </si>
@@ -645,7 +645,87 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>文章列表的第一页是在项目启动的时候就加载了，改成请求时再加载</t>
+    <t>首页</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>待完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌家童</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>文章列表的第一页是在项目启动的时候就加载了，当有更新时应该更新application域中存储的列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消息</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消息滚动</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>首页增加消息滚动功能，效果是上下滚动，后台增加功能消息管理</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>导航菜单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在宽度低的时候点击显示导航菜单，然后将宽度拉大，导航菜单并不会消失，正常情况应该改为消失</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>未解决</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技术文章</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>导航栏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>导航菜单中选中状态的时候，如果鼠标移动到选中状态上的菜单项，应该有颜色暗淡变化，包括搜索按钮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>路径导航</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>路径导航栏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>路径导航栏高度很丑，想办法优化掉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技术文章列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>文章技术列表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>分页查询文章技术列表，路径为/re/articles/type，其中type是类型就查询什么类型的文章列表，文章列表不需要用信息流的形式加载，在列表下方加一个分页栏，显示当前页数和总共有多少页，并且能够进行上一页和下一页跳转</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -818,7 +898,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -874,18 +954,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -902,6 +970,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1345,19 +1431,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" spans="1:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -1398,7 +1484,7 @@
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="28" t="s">
         <v>183</v>
       </c>
       <c r="C3" s="9" t="s">
@@ -1410,8 +1496,8 @@
       <c r="E3" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
+      <c r="F3" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="G3" s="6">
         <v>43861</v>
@@ -1419,17 +1505,19 @@
       <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="I3" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="J3" s="6">
+        <v>43864</v>
+      </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>183</v>
-      </c>
+      <c r="B4" s="29"/>
       <c r="C4" s="9" t="s">
         <v>187</v>
       </c>
@@ -1439,8 +1527,8 @@
       <c r="E4" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
+      <c r="F4" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="G4" s="6">
         <v>43861</v>
@@ -1456,9 +1544,7 @@
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>183</v>
-      </c>
+      <c r="B5" s="29"/>
       <c r="C5" s="9" t="s">
         <v>187</v>
       </c>
@@ -1468,8 +1554,8 @@
       <c r="E5" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
+      <c r="F5" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="G5" s="6">
         <v>43861</v>
@@ -1485,9 +1571,7 @@
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>183</v>
-      </c>
+      <c r="B6" s="29"/>
       <c r="C6" s="9" t="s">
         <v>192</v>
       </c>
@@ -1495,33 +1579,41 @@
         <v>192</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
+        <v>197</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="G6" s="6">
-        <v>43861</v>
+        <v>43866</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>200</v>
+      </c>
       <c r="F7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6">
+        <v>43866</v>
+      </c>
       <c r="H7" s="5" t="s">
         <v>13</v>
       </c>
@@ -1533,10 +1625,16 @@
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>207</v>
+      </c>
       <c r="F8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1552,10 +1650,18 @@
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="B9" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>210</v>
+      </c>
       <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
@@ -1567,14 +1673,20 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>213</v>
+      </c>
       <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
@@ -1590,8 +1702,10 @@
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="9" t="s">
+        <v>212</v>
+      </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
@@ -1609,10 +1723,9 @@
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="5"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
         <v>12</v>
       </c>
@@ -1628,7 +1741,7 @@
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="5"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1853,19 +1966,19 @@
       <c r="K24" s="5"/>
     </row>
     <row r="25" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
     </row>
     <row r="26" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1906,7 +2019,7 @@
       <c r="A27" s="5">
         <v>1</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1939,7 +2052,7 @@
       <c r="A28" s="5">
         <v>2</v>
       </c>
-      <c r="B28" s="20"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1972,7 +2085,7 @@
       <c r="A29" s="5">
         <v>3</v>
       </c>
-      <c r="B29" s="20"/>
+      <c r="B29" s="26"/>
       <c r="C29" s="5" t="s">
         <v>25</v>
       </c>
@@ -2005,7 +2118,7 @@
       <c r="A30" s="5">
         <v>4</v>
       </c>
-      <c r="B30" s="20"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="5" t="s">
         <v>29</v>
       </c>
@@ -2038,7 +2151,7 @@
       <c r="A31" s="5">
         <v>5</v>
       </c>
-      <c r="B31" s="21"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="5" t="s">
         <v>31</v>
       </c>
@@ -2067,10 +2180,10 @@
       <c r="A32" s="5">
         <v>6</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="25" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -2100,8 +2213,8 @@
       <c r="A33" s="5">
         <v>7</v>
       </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
       <c r="D33" s="5" t="s">
         <v>36</v>
       </c>
@@ -2129,8 +2242,8 @@
       <c r="A34" s="5">
         <v>8</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
       <c r="D34" s="5" t="s">
         <v>38</v>
       </c>
@@ -2158,8 +2271,8 @@
       <c r="A35" s="5">
         <v>9</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
       <c r="D35" s="5" t="s">
         <v>40</v>
       </c>
@@ -2183,8 +2296,8 @@
       <c r="A36" s="5">
         <v>10</v>
       </c>
-      <c r="B36" s="20"/>
-      <c r="C36" s="21"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="5" t="s">
         <v>42</v>
       </c>
@@ -2208,7 +2321,7 @@
       <c r="A37" s="5">
         <v>11</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="26"/>
       <c r="C37" s="5" t="s">
         <v>44</v>
       </c>
@@ -2239,10 +2352,10 @@
       <c r="A38" s="5">
         <v>12</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="28" t="s">
         <v>154</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -2272,8 +2385,8 @@
       <c r="A39" s="5">
         <v>13</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
@@ -2301,8 +2414,8 @@
       <c r="A40" s="5">
         <v>14</v>
       </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
       <c r="D40" s="5" t="s">
         <v>52</v>
       </c>
@@ -2332,8 +2445,8 @@
       <c r="A41" s="5">
         <v>15</v>
       </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
       <c r="D41" s="5" t="s">
         <v>55</v>
       </c>
@@ -2363,8 +2476,8 @@
       <c r="A42" s="5">
         <v>16</v>
       </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
       <c r="D42" s="5" t="s">
         <v>57</v>
       </c>
@@ -2392,8 +2505,8 @@
       <c r="A43" s="5">
         <v>17</v>
       </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
       <c r="D43" s="5" t="s">
         <v>59</v>
       </c>
@@ -2421,10 +2534,10 @@
       <c r="A44" s="5">
         <v>18</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="25" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="5" t="s">
@@ -2450,8 +2563,8 @@
       <c r="A45" s="5">
         <v>19</v>
       </c>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
       <c r="D45" s="5" t="s">
         <v>65</v>
       </c>
@@ -2475,8 +2588,8 @@
       <c r="A46" s="5">
         <v>20</v>
       </c>
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
       <c r="D46" s="7" t="s">
         <v>67</v>
       </c>
@@ -2500,8 +2613,8 @@
       <c r="A47" s="5">
         <v>21</v>
       </c>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
       <c r="D47" s="5" t="s">
         <v>69</v>
       </c>
@@ -2525,8 +2638,8 @@
       <c r="A48" s="5">
         <v>22</v>
       </c>
-      <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="27"/>
       <c r="D48" s="5" t="s">
         <v>71</v>
       </c>
@@ -2550,7 +2663,7 @@
       <c r="A49" s="5">
         <v>23</v>
       </c>
-      <c r="B49" s="21"/>
+      <c r="B49" s="27"/>
       <c r="C49" s="5" t="s">
         <v>73</v>
       </c>
@@ -2577,10 +2690,10 @@
       <c r="A50" s="5">
         <v>24</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="25" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -2606,8 +2719,8 @@
       <c r="A51" s="5">
         <v>25</v>
       </c>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
       <c r="D51" s="5" t="s">
         <v>79</v>
       </c>
@@ -2631,8 +2744,8 @@
       <c r="A52" s="5">
         <v>26</v>
       </c>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="5" t="s">
         <v>81</v>
       </c>
@@ -2656,8 +2769,8 @@
       <c r="A53" s="5">
         <v>27</v>
       </c>
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
       <c r="D53" s="5" t="s">
         <v>83</v>
       </c>
@@ -2681,8 +2794,8 @@
       <c r="A54" s="5">
         <v>28</v>
       </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="21"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="27"/>
       <c r="D54" s="5" t="s">
         <v>85</v>
       </c>
@@ -2706,7 +2819,7 @@
       <c r="A55" s="5">
         <v>29</v>
       </c>
-      <c r="B55" s="21"/>
+      <c r="B55" s="27"/>
       <c r="C55" s="5" t="s">
         <v>87</v>
       </c>
@@ -2733,10 +2846,10 @@
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="25" t="s">
         <v>90</v>
       </c>
       <c r="D56" s="5" t="s">
@@ -2766,8 +2879,8 @@
       <c r="A57" s="5">
         <v>31</v>
       </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
       <c r="D57" s="11" t="s">
         <v>159</v>
       </c>
@@ -2795,8 +2908,8 @@
       <c r="A58" s="5">
         <v>32</v>
       </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
       <c r="D58" s="7" t="s">
         <v>93</v>
       </c>
@@ -2824,8 +2937,8 @@
       <c r="A59" s="5">
         <v>33</v>
       </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
       <c r="D59" s="5" t="s">
         <v>95</v>
       </c>
@@ -2853,8 +2966,8 @@
       <c r="A60" s="5">
         <v>34</v>
       </c>
-      <c r="B60" s="20"/>
-      <c r="C60" s="21"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="27"/>
       <c r="D60" s="5" t="s">
         <v>97</v>
       </c>
@@ -2882,7 +2995,7 @@
       <c r="A61" s="5">
         <v>35</v>
       </c>
-      <c r="B61" s="21"/>
+      <c r="B61" s="27"/>
       <c r="C61" s="5" t="s">
         <v>98</v>
       </c>
@@ -2913,10 +3026,10 @@
       <c r="A62" s="5">
         <v>36</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="25" t="s">
         <v>101</v>
       </c>
       <c r="D62" s="5" t="s">
@@ -2946,8 +3059,8 @@
       <c r="A63" s="5">
         <v>37</v>
       </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
       <c r="D63" s="5" t="s">
         <v>103</v>
       </c>
@@ -2975,8 +3088,8 @@
       <c r="A64" s="5">
         <v>38</v>
       </c>
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
       <c r="D64" s="5" t="s">
         <v>104</v>
       </c>
@@ -3004,8 +3117,8 @@
       <c r="A65" s="5">
         <v>39</v>
       </c>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
       <c r="D65" s="5" t="s">
         <v>105</v>
       </c>
@@ -3033,8 +3146,8 @@
       <c r="A66" s="5">
         <v>40</v>
       </c>
-      <c r="B66" s="20"/>
-      <c r="C66" s="21"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="27"/>
       <c r="D66" s="5" t="s">
         <v>106</v>
       </c>
@@ -3062,7 +3175,7 @@
       <c r="A67" s="5">
         <v>41</v>
       </c>
-      <c r="B67" s="21"/>
+      <c r="B67" s="27"/>
       <c r="C67" s="5" t="s">
         <v>107</v>
       </c>
@@ -3093,10 +3206,10 @@
       <c r="A68" s="5">
         <v>42</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="B68" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="C68" s="25" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="5" t="s">
@@ -3126,8 +3239,8 @@
       <c r="A69" s="5">
         <v>43</v>
       </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
       <c r="D69" s="5" t="s">
         <v>112</v>
       </c>
@@ -3155,8 +3268,8 @@
       <c r="A70" s="5">
         <v>44</v>
       </c>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
       <c r="D70" s="5" t="s">
         <v>114</v>
       </c>
@@ -3184,8 +3297,8 @@
       <c r="A71" s="5">
         <v>45</v>
       </c>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="5" t="s">
         <v>115</v>
       </c>
@@ -3213,8 +3326,8 @@
       <c r="A72" s="5">
         <v>46</v>
       </c>
-      <c r="B72" s="20"/>
-      <c r="C72" s="21"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="27"/>
       <c r="D72" s="5" t="s">
         <v>117</v>
       </c>
@@ -3242,7 +3355,7 @@
       <c r="A73" s="5">
         <v>47</v>
       </c>
-      <c r="B73" s="21"/>
+      <c r="B73" s="27"/>
       <c r="C73" s="5" t="s">
         <v>118</v>
       </c>
@@ -3273,10 +3386,10 @@
       <c r="A74" s="5">
         <v>48</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C74" s="25" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="5" t="s">
@@ -3306,8 +3419,8 @@
       <c r="A75" s="5">
         <v>49</v>
       </c>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
       <c r="D75" s="9" t="s">
         <v>166</v>
       </c>
@@ -3335,8 +3448,8 @@
       <c r="A76" s="5">
         <v>50</v>
       </c>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
       <c r="D76" s="5" t="s">
         <v>123</v>
       </c>
@@ -3364,8 +3477,8 @@
       <c r="A77" s="5">
         <v>51</v>
       </c>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
       <c r="D77" s="5" t="s">
         <v>124</v>
       </c>
@@ -3393,8 +3506,8 @@
       <c r="A78" s="5">
         <v>52</v>
       </c>
-      <c r="B78" s="20"/>
-      <c r="C78" s="21"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="27"/>
       <c r="D78" s="5" t="s">
         <v>126</v>
       </c>
@@ -3422,7 +3535,7 @@
       <c r="A79" s="5">
         <v>53</v>
       </c>
-      <c r="B79" s="21"/>
+      <c r="B79" s="27"/>
       <c r="C79" s="5" t="s">
         <v>127</v>
       </c>
@@ -3453,10 +3566,10 @@
       <c r="A80" s="5">
         <v>54</v>
       </c>
-      <c r="B80" s="19" t="s">
+      <c r="B80" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="25" t="s">
         <v>130</v>
       </c>
       <c r="D80" s="5" t="s">
@@ -3486,8 +3599,8 @@
       <c r="A81" s="5">
         <v>55</v>
       </c>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
       <c r="D81" s="5" t="s">
         <v>131</v>
       </c>
@@ -3515,8 +3628,8 @@
       <c r="A82" s="5">
         <v>56</v>
       </c>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
       <c r="D82" s="5" t="s">
         <v>132</v>
       </c>
@@ -3544,8 +3657,8 @@
       <c r="A83" s="5">
         <v>57</v>
       </c>
-      <c r="B83" s="20"/>
-      <c r="C83" s="20"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
       <c r="D83" s="5" t="s">
         <v>133</v>
       </c>
@@ -3573,8 +3686,8 @@
       <c r="A84" s="5">
         <v>58</v>
       </c>
-      <c r="B84" s="20"/>
-      <c r="C84" s="21"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="27"/>
       <c r="D84" s="5" t="s">
         <v>134</v>
       </c>
@@ -3602,7 +3715,7 @@
       <c r="A85" s="5">
         <v>59</v>
       </c>
-      <c r="B85" s="21"/>
+      <c r="B85" s="27"/>
       <c r="C85" s="5" t="s">
         <v>135</v>
       </c>
@@ -3633,10 +3746,10 @@
       <c r="A86" s="5">
         <v>60</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="C86" s="19" t="s">
+      <c r="C86" s="25" t="s">
         <v>138</v>
       </c>
       <c r="D86" s="5" t="s">
@@ -3666,8 +3779,8 @@
       <c r="A87" s="5">
         <v>61</v>
       </c>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
       <c r="D87" s="5" t="s">
         <v>140</v>
       </c>
@@ -3695,8 +3808,8 @@
       <c r="A88" s="5">
         <v>62</v>
       </c>
-      <c r="B88" s="20"/>
-      <c r="C88" s="20"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
       <c r="D88" s="5" t="s">
         <v>141</v>
       </c>
@@ -3724,8 +3837,8 @@
       <c r="A89" s="5">
         <v>63</v>
       </c>
-      <c r="B89" s="20"/>
-      <c r="C89" s="20"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
       <c r="D89" s="5" t="s">
         <v>142</v>
       </c>
@@ -3753,8 +3866,8 @@
       <c r="A90" s="5">
         <v>64</v>
       </c>
-      <c r="B90" s="20"/>
-      <c r="C90" s="21"/>
+      <c r="B90" s="26"/>
+      <c r="C90" s="27"/>
       <c r="D90" s="5" t="s">
         <v>144</v>
       </c>
@@ -3782,7 +3895,7 @@
       <c r="A91" s="5">
         <v>65</v>
       </c>
-      <c r="B91" s="21"/>
+      <c r="B91" s="27"/>
       <c r="C91" s="5" t="s">
         <v>145</v>
       </c>
@@ -3835,19 +3948,19 @@
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="27" t="s">
+      <c r="A97" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="B97" s="28"/>
-      <c r="C97" s="28"/>
-      <c r="D97" s="28"/>
-      <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="28"/>
-      <c r="J97" s="28"/>
-      <c r="K97" s="28"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="24"/>
+      <c r="I97" s="24"/>
+      <c r="J97" s="24"/>
+      <c r="K97" s="24"/>
     </row>
     <row r="98" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
@@ -3936,10 +4049,45 @@
         <v>182</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="3">
+        <v>3</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D101" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E101" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F101" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="G101" s="8">
+        <v>43866</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
     <row r="102" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C38:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="C62:C66"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A25:K25"/>
     <mergeCell ref="A97:K97"/>
@@ -3956,14 +4104,6 @@
     <mergeCell ref="B86:B91"/>
     <mergeCell ref="C32:C36"/>
     <mergeCell ref="C68:C72"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C38:C43"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="C62:C66"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
